--- a/Intake_Mexico_v1.xlsx
+++ b/Intake_Mexico_v1.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AD86"/>
+  <dimension ref="B1:AD102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -848,47 +848,47 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Res Building</t>
+          <t>Res Building (optional)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Res Content</t>
+          <t>Res Content (optional)</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Res BI</t>
+          <t>Res BI (optional)</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Com Building</t>
+          <t>Com Building (optional)</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Com Content</t>
+          <t>Com Content (optional)</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Com BI</t>
+          <t>Com BI (optional)</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Ind Building</t>
+          <t>Ind Building (optional)</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Ind Content</t>
+          <t>Ind Content (optional)</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Ind BI</t>
+          <t>Ind BI (optional)</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
@@ -985,50 +985,20 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Res Building</t>
+          <t>Res (optional)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Res Content</t>
+          <t>Com (optional)</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Res BI</t>
+          <t>Ind (optional)</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>Com Building</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>Com Content</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Com BI</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Ind Building</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>Ind Content</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Ind BI</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>Total (optional)</t>
         </is>
@@ -1498,295 +1468,556 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Com</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
     <row r="56">
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="7" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Zone scheme</t>
+          <t>Share basis</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Mexico EQ | Mexico Wind</t>
+          <t>100% | ceded only</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Coinsurance</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>deducted | not deducted</t>
+          <t>1 | 1,000 | 1,000,000</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Deductible</t>
+          <t>Exposure basis</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>deducted | not deducted</t>
+          <t>Sum Insured | EML | PML | MPL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Limit basis</t>
+          <t>Zone scheme</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>full sum insured | per risk limit | per location limit</t>
+          <t>Mexico EQ | Mexico Wind</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Multi-location</t>
+          <t>Coinsurance</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>split by location | allocated to main zone | duplicated in each zone</t>
+          <t>deducted | not deducted</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Includes fac</t>
+          <t>Deductible</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>yes | no</t>
+          <t>deducted | not deducted</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="4" t="inlineStr">
         <is>
+          <t>Limit basis</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>full sum insured | per risk limit | per location limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Multi-location</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>split by location | allocated to main zone | duplicated in each zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Includes fac</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>yes | no</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="3" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="7" t="inlineStr">
+    <row r="77">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>Suffix</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>9 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>re-est</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>at inception</t>
+          <t>est</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>re-est</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>at inception</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>at expiry</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="2" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>'at inception' and 'at expiry' order the three versions of an aggregate: the nine-month estimate of N, then the first and the last day of N+1.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="3" t="inlineStr">
+    <row r="86">
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>⟦AXES⟧</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>06 EQ Aggs</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Res, Com, Ind</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>06 EQ Aggs</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Building, Content, BI</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>07 Wind Aggs</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Res, Com, Ind</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>The buckets of a dataset are the product of its axes: earthquake is occupancy × cover and has nine, hurricane declares occupancy alone and has three.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>⟦SPLITS⟧</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Scheme</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>07 Wind Aggs</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="F84" s="7" t="inlineStr">
-        <is>
-          <t>BI</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Empty by design. Where a cedent sends fewer buckets than the nine, the ratios that fill the rest go here — declared, visible and versioned with the pack, because a split is an assumption and not a reading.</t>
+      <c r="D96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Cedent book split, 30.09.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>07 Wind Aggs</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Com</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>Cedent book split, 30.09.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>07 Wind Aggs</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Cedent book split, 30.09.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Com</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>House convention</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>House convention</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Ratios applied where the cedent reports at a coarser level. A blank 'From' distributes a whole axis; a filled one re-splits a category that arrived merged. 'Source' is not decoration — a ratio from the cedent's own prior submission and one borrowed from another book are both assumptions, but not equally good ones.</t>
         </is>
       </c>
     </row>
@@ -2714,16 +2945,16 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="46" customWidth="1" min="15" max="15"/>
   </cols>
@@ -9863,16 +10094,7 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="46" customWidth="1" min="15" max="15"/>
   </cols>
@@ -9887,7 +10109,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Three versions of the same zoning. The movement between them is the point — see the growth block written beneath.</t>
+          <t>Three versions, reported as one figure per zone. The occupancy split comes from sheet 00 ⟦SPLITS⟧ — see the notes in step 2.</t>
         </is>
       </c>
     </row>
@@ -10002,52 +10224,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Res edif.</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Res cont.</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>Res PB</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>Com edif.</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>Com cont.</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>Com PB</t>
-        </is>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>Ind edif.</t>
-        </is>
-      </c>
-      <c r="J17" s="12" t="inlineStr">
-        <is>
-          <t>Ind cont.</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>Ind PB</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>Suma</t>
+          <t>Suma asegurada</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -10069,51 +10246,6 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Res Building</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Res Content</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Res BI</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>Com Building</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>Com Content</t>
-        </is>
-      </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>Com BI</t>
-        </is>
-      </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>Ind Building</t>
-        </is>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
-        <is>
-          <t>Ind Content</t>
-        </is>
-      </c>
-      <c r="K18" s="14" t="inlineStr">
-        <is>
-          <t>Ind BI</t>
-        </is>
-      </c>
-      <c r="L18" s="14" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -10130,33 +10262,6 @@
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>521</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>136</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>248</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>74</v>
-      </c>
-      <c r="H19" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="I19" s="16" t="n">
-        <v>124</v>
-      </c>
-      <c r="J19" s="16" t="n">
-        <v>37</v>
-      </c>
-      <c r="K19" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="L19" s="16" t="n">
         <v>1240</v>
       </c>
       <c r="N19" s="17">
@@ -10171,33 +10276,6 @@
         </is>
       </c>
       <c r="C20" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>36</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>1035</v>
-      </c>
-      <c r="G20" s="16" t="n">
-        <v>321</v>
-      </c>
-      <c r="H20" s="16" t="n">
-        <v>214</v>
-      </c>
-      <c r="I20" s="16" t="n">
-        <v>500</v>
-      </c>
-      <c r="J20" s="16" t="n">
-        <v>143</v>
-      </c>
-      <c r="K20" s="16" t="n">
-        <v>71</v>
-      </c>
-      <c r="L20" s="16" t="n">
         <v>3570</v>
       </c>
       <c r="N20" s="17">
@@ -10212,33 +10290,6 @@
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>3203</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>801</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>160</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>6085</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>1762</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <v>1281</v>
-      </c>
-      <c r="I21" s="16" t="n">
-        <v>1922</v>
-      </c>
-      <c r="J21" s="16" t="n">
-        <v>480</v>
-      </c>
-      <c r="K21" s="16" t="n">
-        <v>320</v>
-      </c>
-      <c r="L21" s="16" t="n">
         <v>16014</v>
       </c>
       <c r="N21" s="17">
@@ -10253,33 +10304,6 @@
         </is>
       </c>
       <c r="C22" s="16" t="n">
-        <v>916</v>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>44</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>436</v>
-      </c>
-      <c r="G22" s="16" t="n">
-        <v>131</v>
-      </c>
-      <c r="H22" s="16" t="n">
-        <v>87</v>
-      </c>
-      <c r="I22" s="16" t="n">
-        <v>218</v>
-      </c>
-      <c r="J22" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="K22" s="16" t="n">
-        <v>44</v>
-      </c>
-      <c r="L22" s="16" t="n">
         <v>2181</v>
       </c>
       <c r="N22" s="17">
@@ -10294,33 +10318,6 @@
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>1490</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>372</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>53</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>1543</v>
-      </c>
-      <c r="G23" s="16" t="n">
-        <v>479</v>
-      </c>
-      <c r="H23" s="16" t="n">
-        <v>319</v>
-      </c>
-      <c r="I23" s="16" t="n">
-        <v>745</v>
-      </c>
-      <c r="J23" s="16" t="n">
-        <v>213</v>
-      </c>
-      <c r="K23" s="16" t="n">
-        <v>106</v>
-      </c>
-      <c r="L23" s="16" t="n">
         <v>5320</v>
       </c>
       <c r="N23" s="17">
@@ -10335,33 +10332,6 @@
         </is>
       </c>
       <c r="C24" s="16" t="n">
-        <v>739</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>194</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>352</v>
-      </c>
-      <c r="G24" s="16" t="n">
-        <v>106</v>
-      </c>
-      <c r="H24" s="16" t="n">
-        <v>70</v>
-      </c>
-      <c r="I24" s="16" t="n">
-        <v>176</v>
-      </c>
-      <c r="J24" s="16" t="n">
-        <v>53</v>
-      </c>
-      <c r="K24" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="L24" s="16" t="n">
         <v>1760</v>
       </c>
       <c r="N24" s="17">
@@ -10376,33 +10346,6 @@
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>6418</v>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>1604</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>321</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>12194</v>
-      </c>
-      <c r="G25" s="16" t="n">
-        <v>3530</v>
-      </c>
-      <c r="H25" s="16" t="n">
-        <v>2567</v>
-      </c>
-      <c r="I25" s="16" t="n">
-        <v>3851</v>
-      </c>
-      <c r="J25" s="16" t="n">
-        <v>963</v>
-      </c>
-      <c r="K25" s="16" t="n">
-        <v>642</v>
-      </c>
-      <c r="L25" s="16" t="n">
         <v>32090</v>
       </c>
       <c r="N25" s="17">
@@ -10417,33 +10360,6 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>645</v>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>184</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>830</v>
-      </c>
-      <c r="G26" s="16" t="n">
-        <v>230</v>
-      </c>
-      <c r="H26" s="16" t="n">
-        <v>184</v>
-      </c>
-      <c r="I26" s="16" t="n">
-        <v>1660</v>
-      </c>
-      <c r="J26" s="16" t="n">
-        <v>507</v>
-      </c>
-      <c r="K26" s="16" t="n">
-        <v>323</v>
-      </c>
-      <c r="L26" s="16" t="n">
         <v>4609</v>
       </c>
       <c r="N26" s="17">
@@ -10458,33 +10374,6 @@
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>941</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>246</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>448</v>
-      </c>
-      <c r="G27" s="16" t="n">
-        <v>134</v>
-      </c>
-      <c r="H27" s="16" t="n">
-        <v>90</v>
-      </c>
-      <c r="I27" s="16" t="n">
-        <v>224</v>
-      </c>
-      <c r="J27" s="16" t="n">
-        <v>67</v>
-      </c>
-      <c r="K27" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="L27" s="16" t="n">
         <v>2240</v>
       </c>
       <c r="N27" s="17">
@@ -10499,33 +10388,6 @@
         </is>
       </c>
       <c r="C28" s="16" t="n">
-        <v>1924</v>
-      </c>
-      <c r="D28" s="16" t="n">
-        <v>481</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>69</v>
-      </c>
-      <c r="F28" s="16" t="n">
-        <v>1992</v>
-      </c>
-      <c r="G28" s="16" t="n">
-        <v>618</v>
-      </c>
-      <c r="H28" s="16" t="n">
-        <v>412</v>
-      </c>
-      <c r="I28" s="16" t="n">
-        <v>962</v>
-      </c>
-      <c r="J28" s="16" t="n">
-        <v>275</v>
-      </c>
-      <c r="K28" s="16" t="n">
-        <v>137</v>
-      </c>
-      <c r="L28" s="16" t="n">
         <v>6870</v>
       </c>
       <c r="N28" s="17">
@@ -10540,33 +10402,6 @@
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>584</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>153</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>278</v>
-      </c>
-      <c r="G29" s="16" t="n">
-        <v>83</v>
-      </c>
-      <c r="H29" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="I29" s="16" t="n">
-        <v>139</v>
-      </c>
-      <c r="J29" s="16" t="n">
-        <v>42</v>
-      </c>
-      <c r="K29" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="L29" s="16" t="n">
         <v>1391</v>
       </c>
       <c r="N29" s="17">
@@ -10581,33 +10416,6 @@
         </is>
       </c>
       <c r="C30" s="16" t="n">
-        <v>1576</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>394</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>79</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>2994</v>
-      </c>
-      <c r="G30" s="16" t="n">
-        <v>867</v>
-      </c>
-      <c r="H30" s="16" t="n">
-        <v>630</v>
-      </c>
-      <c r="I30" s="16" t="n">
-        <v>945</v>
-      </c>
-      <c r="J30" s="16" t="n">
-        <v>236</v>
-      </c>
-      <c r="K30" s="16" t="n">
-        <v>158</v>
-      </c>
-      <c r="L30" s="16" t="n">
         <v>7879</v>
       </c>
       <c r="N30" s="17">
@@ -10622,33 +10430,6 @@
         </is>
       </c>
       <c r="C31" s="16" t="n">
-        <v>854</v>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>214</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>884</v>
-      </c>
-      <c r="G31" s="16" t="n">
-        <v>274</v>
-      </c>
-      <c r="H31" s="16" t="n">
-        <v>183</v>
-      </c>
-      <c r="I31" s="16" t="n">
-        <v>427</v>
-      </c>
-      <c r="J31" s="16" t="n">
-        <v>122</v>
-      </c>
-      <c r="K31" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="L31" s="16" t="n">
         <v>3049</v>
       </c>
       <c r="N31" s="17">
@@ -10665,33 +10446,6 @@
       <c r="C32" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="16" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" s="17">
         <f>ROW()</f>
         <v>32</v>
@@ -10704,33 +10458,6 @@
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>1109</v>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>290</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>53</v>
-      </c>
-      <c r="F33" s="16" t="n">
-        <v>528</v>
-      </c>
-      <c r="G33" s="16" t="n">
-        <v>158</v>
-      </c>
-      <c r="H33" s="16" t="n">
-        <v>106</v>
-      </c>
-      <c r="I33" s="16" t="n">
-        <v>264</v>
-      </c>
-      <c r="J33" s="16" t="n">
-        <v>79</v>
-      </c>
-      <c r="K33" s="16" t="n">
-        <v>53</v>
-      </c>
-      <c r="L33" s="16" t="n">
         <v>2640</v>
       </c>
       <c r="N33" s="17">
@@ -10745,33 +10472,6 @@
         </is>
       </c>
       <c r="C34" s="16" t="n">
-        <v>1028</v>
-      </c>
-      <c r="D34" s="16" t="n">
-        <v>257</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>51</v>
-      </c>
-      <c r="F34" s="16" t="n">
-        <v>1953</v>
-      </c>
-      <c r="G34" s="16" t="n">
-        <v>565</v>
-      </c>
-      <c r="H34" s="16" t="n">
-        <v>411</v>
-      </c>
-      <c r="I34" s="16" t="n">
-        <v>617</v>
-      </c>
-      <c r="J34" s="16" t="n">
-        <v>154</v>
-      </c>
-      <c r="K34" s="16" t="n">
-        <v>103</v>
-      </c>
-      <c r="L34" s="16" t="n">
         <v>5139</v>
       </c>
       <c r="N34" s="17">
@@ -10786,33 +10486,6 @@
         </is>
       </c>
       <c r="C35" s="16" t="n">
-        <v>255</v>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>73</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="F35" s="16" t="n">
-        <v>328</v>
-      </c>
-      <c r="G35" s="16" t="n">
-        <v>91</v>
-      </c>
-      <c r="H35" s="16" t="n">
-        <v>73</v>
-      </c>
-      <c r="I35" s="16" t="n">
-        <v>655</v>
-      </c>
-      <c r="J35" s="16" t="n">
-        <v>200</v>
-      </c>
-      <c r="K35" s="16" t="n">
-        <v>127</v>
-      </c>
-      <c r="L35" s="16" t="n">
         <v>1820</v>
       </c>
       <c r="N35" s="17">
@@ -10827,33 +10500,6 @@
         </is>
       </c>
       <c r="C36" s="16" t="n">
-        <v>1109</v>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>277</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="F36" s="16" t="n">
-        <v>1148</v>
-      </c>
-      <c r="G36" s="16" t="n">
-        <v>356</v>
-      </c>
-      <c r="H36" s="16" t="n">
-        <v>238</v>
-      </c>
-      <c r="I36" s="16" t="n">
-        <v>554</v>
-      </c>
-      <c r="J36" s="16" t="n">
-        <v>158</v>
-      </c>
-      <c r="K36" s="16" t="n">
-        <v>79</v>
-      </c>
-      <c r="L36" s="16" t="n">
         <v>3959</v>
       </c>
       <c r="N36" s="17">
@@ -10868,33 +10514,6 @@
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>4642</v>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>1160</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>232</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>8819</v>
-      </c>
-      <c r="G37" s="16" t="n">
-        <v>2553</v>
-      </c>
-      <c r="H37" s="16" t="n">
-        <v>1857</v>
-      </c>
-      <c r="I37" s="16" t="n">
-        <v>2785</v>
-      </c>
-      <c r="J37" s="16" t="n">
-        <v>696</v>
-      </c>
-      <c r="K37" s="16" t="n">
-        <v>464</v>
-      </c>
-      <c r="L37" s="16" t="n">
         <v>23208</v>
       </c>
       <c r="N37" s="17">
@@ -10909,33 +10528,6 @@
         </is>
       </c>
       <c r="C38" s="16" t="n">
-        <v>1037</v>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>272</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="F38" s="16" t="n">
-        <v>494</v>
-      </c>
-      <c r="G38" s="16" t="n">
-        <v>148</v>
-      </c>
-      <c r="H38" s="16" t="n">
-        <v>99</v>
-      </c>
-      <c r="I38" s="16" t="n">
-        <v>247</v>
-      </c>
-      <c r="J38" s="16" t="n">
-        <v>74</v>
-      </c>
-      <c r="K38" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="L38" s="16" t="n">
         <v>2469</v>
       </c>
       <c r="N38" s="17">
@@ -10950,33 +10542,6 @@
         </is>
       </c>
       <c r="C39" s="16" t="n">
-        <v>1767</v>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>442</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>63</v>
-      </c>
-      <c r="F39" s="16" t="n">
-        <v>1830</v>
-      </c>
-      <c r="G39" s="16" t="n">
-        <v>568</v>
-      </c>
-      <c r="H39" s="16" t="n">
-        <v>379</v>
-      </c>
-      <c r="I39" s="16" t="n">
-        <v>883</v>
-      </c>
-      <c r="J39" s="16" t="n">
-        <v>252</v>
-      </c>
-      <c r="K39" s="16" t="n">
-        <v>126</v>
-      </c>
-      <c r="L39" s="16" t="n">
         <v>6310</v>
       </c>
       <c r="N39" s="17">
@@ -10991,33 +10556,6 @@
         </is>
       </c>
       <c r="C40" s="16" t="n">
-        <v>664</v>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>174</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="F40" s="16" t="n">
-        <v>316</v>
-      </c>
-      <c r="G40" s="16" t="n">
-        <v>95</v>
-      </c>
-      <c r="H40" s="16" t="n">
-        <v>63</v>
-      </c>
-      <c r="I40" s="16" t="n">
-        <v>158</v>
-      </c>
-      <c r="J40" s="16" t="n">
-        <v>47</v>
-      </c>
-      <c r="K40" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="L40" s="16" t="n">
         <v>1581</v>
       </c>
       <c r="N40" s="17">
@@ -11032,33 +10570,6 @@
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>592</v>
-      </c>
-      <c r="D41" s="16" t="n">
-        <v>169</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>42</v>
-      </c>
-      <c r="F41" s="16" t="n">
-        <v>761</v>
-      </c>
-      <c r="G41" s="16" t="n">
-        <v>212</v>
-      </c>
-      <c r="H41" s="16" t="n">
-        <v>169</v>
-      </c>
-      <c r="I41" s="16" t="n">
-        <v>1523</v>
-      </c>
-      <c r="J41" s="16" t="n">
-        <v>465</v>
-      </c>
-      <c r="K41" s="16" t="n">
-        <v>296</v>
-      </c>
-      <c r="L41" s="16" t="n">
         <v>4229</v>
       </c>
       <c r="N41" s="17">
@@ -11073,33 +10584,6 @@
         </is>
       </c>
       <c r="C42" s="16" t="n">
-        <v>578</v>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>144</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>1098</v>
-      </c>
-      <c r="G42" s="16" t="n">
-        <v>318</v>
-      </c>
-      <c r="H42" s="16" t="n">
-        <v>231</v>
-      </c>
-      <c r="I42" s="16" t="n">
-        <v>347</v>
-      </c>
-      <c r="J42" s="16" t="n">
-        <v>87</v>
-      </c>
-      <c r="K42" s="16" t="n">
-        <v>58</v>
-      </c>
-      <c r="L42" s="16" t="n">
         <v>2890</v>
       </c>
       <c r="N42" s="17">
@@ -11114,33 +10598,6 @@
         </is>
       </c>
       <c r="C43" s="16" t="n">
-        <v>563</v>
-      </c>
-      <c r="D43" s="16" t="n">
-        <v>147</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="F43" s="16" t="n">
-        <v>268</v>
-      </c>
-      <c r="G43" s="16" t="n">
-        <v>80</v>
-      </c>
-      <c r="H43" s="16" t="n">
-        <v>54</v>
-      </c>
-      <c r="I43" s="16" t="n">
-        <v>134</v>
-      </c>
-      <c r="J43" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="K43" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="L43" s="16" t="n">
         <v>1340</v>
       </c>
       <c r="N43" s="17">
@@ -11155,33 +10612,6 @@
         </is>
       </c>
       <c r="C44" s="16" t="n">
-        <v>1613</v>
-      </c>
-      <c r="D44" s="16" t="n">
-        <v>403</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>58</v>
-      </c>
-      <c r="F44" s="16" t="n">
-        <v>1670</v>
-      </c>
-      <c r="G44" s="16" t="n">
-        <v>518</v>
-      </c>
-      <c r="H44" s="16" t="n">
-        <v>346</v>
-      </c>
-      <c r="I44" s="16" t="n">
-        <v>806</v>
-      </c>
-      <c r="J44" s="16" t="n">
-        <v>230</v>
-      </c>
-      <c r="K44" s="16" t="n">
-        <v>115</v>
-      </c>
-      <c r="L44" s="16" t="n">
         <v>5759</v>
       </c>
       <c r="N44" s="17">
@@ -11196,33 +10626,6 @@
         </is>
       </c>
       <c r="C45" s="16" t="n">
-        <v>865</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>227</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>41</v>
-      </c>
-      <c r="F45" s="16" t="n">
-        <v>412</v>
-      </c>
-      <c r="G45" s="16" t="n">
-        <v>124</v>
-      </c>
-      <c r="H45" s="16" t="n">
-        <v>82</v>
-      </c>
-      <c r="I45" s="16" t="n">
-        <v>206</v>
-      </c>
-      <c r="J45" s="16" t="n">
-        <v>62</v>
-      </c>
-      <c r="K45" s="16" t="n">
-        <v>41</v>
-      </c>
-      <c r="L45" s="16" t="n">
         <v>2060</v>
       </c>
       <c r="N45" s="17">
@@ -11237,33 +10640,6 @@
         </is>
       </c>
       <c r="C46" s="16" t="n">
-        <v>1702</v>
-      </c>
-      <c r="D46" s="16" t="n">
-        <v>446</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>81</v>
-      </c>
-      <c r="F46" s="16" t="n">
-        <v>810</v>
-      </c>
-      <c r="G46" s="16" t="n">
-        <v>243</v>
-      </c>
-      <c r="H46" s="16" t="n">
-        <v>162</v>
-      </c>
-      <c r="I46" s="16" t="n">
-        <v>405</v>
-      </c>
-      <c r="J46" s="16" t="n">
-        <v>122</v>
-      </c>
-      <c r="K46" s="16" t="n">
-        <v>81</v>
-      </c>
-      <c r="L46" s="16" t="n">
         <v>4052</v>
       </c>
       <c r="N46" s="17">
@@ -11278,33 +10654,6 @@
         </is>
       </c>
       <c r="C47" s="16" t="n">
-        <v>682</v>
-      </c>
-      <c r="D47" s="16" t="n">
-        <v>170</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="F47" s="16" t="n">
-        <v>1296</v>
-      </c>
-      <c r="G47" s="16" t="n">
-        <v>375</v>
-      </c>
-      <c r="H47" s="16" t="n">
-        <v>273</v>
-      </c>
-      <c r="I47" s="16" t="n">
-        <v>409</v>
-      </c>
-      <c r="J47" s="16" t="n">
-        <v>102</v>
-      </c>
-      <c r="K47" s="16" t="n">
-        <v>68</v>
-      </c>
-      <c r="L47" s="16" t="n">
         <v>3409</v>
       </c>
       <c r="N47" s="17">
@@ -11319,33 +10668,6 @@
         </is>
       </c>
       <c r="C48" s="16" t="n">
-        <v>234</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>67</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="F48" s="16" t="n">
-        <v>301</v>
-      </c>
-      <c r="G48" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="H48" s="16" t="n">
-        <v>67</v>
-      </c>
-      <c r="I48" s="16" t="n">
-        <v>601</v>
-      </c>
-      <c r="J48" s="16" t="n">
-        <v>184</v>
-      </c>
-      <c r="K48" s="16" t="n">
-        <v>117</v>
-      </c>
-      <c r="L48" s="16" t="n">
         <v>1672</v>
       </c>
       <c r="N48" s="17">
@@ -11360,33 +10682,6 @@
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>1831</v>
-      </c>
-      <c r="D49" s="16" t="n">
-        <v>458</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="F49" s="16" t="n">
-        <v>1897</v>
-      </c>
-      <c r="G49" s="16" t="n">
-        <v>589</v>
-      </c>
-      <c r="H49" s="16" t="n">
-        <v>392</v>
-      </c>
-      <c r="I49" s="16" t="n">
-        <v>916</v>
-      </c>
-      <c r="J49" s="16" t="n">
-        <v>262</v>
-      </c>
-      <c r="K49" s="16" t="n">
-        <v>131</v>
-      </c>
-      <c r="L49" s="16" t="n">
         <v>6541</v>
       </c>
       <c r="N49" s="17">
@@ -11401,33 +10696,6 @@
         </is>
       </c>
       <c r="C50" s="16" t="n">
-        <v>974</v>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>255</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="F50" s="16" t="n">
-        <v>464</v>
-      </c>
-      <c r="G50" s="16" t="n">
-        <v>139</v>
-      </c>
-      <c r="H50" s="16" t="n">
-        <v>93</v>
-      </c>
-      <c r="I50" s="16" t="n">
-        <v>232</v>
-      </c>
-      <c r="J50" s="16" t="n">
-        <v>70</v>
-      </c>
-      <c r="K50" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="L50" s="16" t="n">
         <v>2319</v>
       </c>
       <c r="N50" s="17">
@@ -11442,33 +10710,6 @@
         </is>
       </c>
       <c r="C51" s="16" t="n">
-        <v>978</v>
-      </c>
-      <c r="D51" s="16" t="n">
-        <v>244</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="F51" s="16" t="n">
-        <v>1858</v>
-      </c>
-      <c r="G51" s="16" t="n">
-        <v>538</v>
-      </c>
-      <c r="H51" s="16" t="n">
-        <v>391</v>
-      </c>
-      <c r="I51" s="16" t="n">
-        <v>587</v>
-      </c>
-      <c r="J51" s="16" t="n">
-        <v>147</v>
-      </c>
-      <c r="K51" s="16" t="n">
-        <v>98</v>
-      </c>
-      <c r="L51" s="16" t="n">
         <v>4890</v>
       </c>
       <c r="N51" s="17">
@@ -11483,33 +10724,6 @@
         </is>
       </c>
       <c r="C52" s="16" t="n">
-        <v>609</v>
-      </c>
-      <c r="D52" s="16" t="n">
-        <v>160</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="F52" s="16" t="n">
-        <v>290</v>
-      </c>
-      <c r="G52" s="16" t="n">
-        <v>87</v>
-      </c>
-      <c r="H52" s="16" t="n">
-        <v>58</v>
-      </c>
-      <c r="I52" s="16" t="n">
-        <v>145</v>
-      </c>
-      <c r="J52" s="16" t="n">
-        <v>44</v>
-      </c>
-      <c r="K52" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="L52" s="16" t="n">
         <v>1451</v>
       </c>
       <c r="N52" s="17">
@@ -11524,33 +10738,6 @@
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>890</v>
-      </c>
-      <c r="D53" s="16" t="n">
-        <v>223</v>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="F53" s="16" t="n">
-        <v>922</v>
-      </c>
-      <c r="G53" s="16" t="n">
-        <v>286</v>
-      </c>
-      <c r="H53" s="16" t="n">
-        <v>191</v>
-      </c>
-      <c r="I53" s="16" t="n">
-        <v>445</v>
-      </c>
-      <c r="J53" s="16" t="n">
-        <v>127</v>
-      </c>
-      <c r="K53" s="16" t="n">
-        <v>64</v>
-      </c>
-      <c r="L53" s="16" t="n">
         <v>3180</v>
       </c>
       <c r="N53" s="17">
@@ -11567,33 +10754,6 @@
       <c r="C54" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D54" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="16" t="n">
-        <v>0</v>
-      </c>
       <c r="N54" s="17">
         <f>ROW()</f>
         <v>54</v>
@@ -11606,33 +10766,6 @@
         </is>
       </c>
       <c r="C55" s="16" t="n">
-        <v>1086</v>
-      </c>
-      <c r="D55" s="16" t="n">
-        <v>272</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>54</v>
-      </c>
-      <c r="F55" s="16" t="n">
-        <v>2063</v>
-      </c>
-      <c r="G55" s="16" t="n">
-        <v>597</v>
-      </c>
-      <c r="H55" s="16" t="n">
-        <v>434</v>
-      </c>
-      <c r="I55" s="16" t="n">
-        <v>652</v>
-      </c>
-      <c r="J55" s="16" t="n">
-        <v>163</v>
-      </c>
-      <c r="K55" s="16" t="n">
-        <v>109</v>
-      </c>
-      <c r="L55" s="16" t="n">
         <v>5430</v>
       </c>
       <c r="N55" s="17">
@@ -11647,33 +10780,6 @@
         </is>
       </c>
       <c r="C56" s="16" t="n">
-        <v>1138</v>
-      </c>
-      <c r="D56" s="16" t="n">
-        <v>298</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>54</v>
-      </c>
-      <c r="F56" s="16" t="n">
-        <v>542</v>
-      </c>
-      <c r="G56" s="16" t="n">
-        <v>163</v>
-      </c>
-      <c r="H56" s="16" t="n">
-        <v>108</v>
-      </c>
-      <c r="I56" s="16" t="n">
-        <v>271</v>
-      </c>
-      <c r="J56" s="16" t="n">
-        <v>81</v>
-      </c>
-      <c r="K56" s="16" t="n">
-        <v>54</v>
-      </c>
-      <c r="L56" s="16" t="n">
         <v>2709</v>
       </c>
       <c r="N56" s="17">
@@ -11688,33 +10794,6 @@
         </is>
       </c>
       <c r="C57" s="16" t="n">
-        <v>274</v>
-      </c>
-      <c r="D57" s="16" t="n">
-        <v>78</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>353</v>
-      </c>
-      <c r="G57" s="16" t="n">
-        <v>98</v>
-      </c>
-      <c r="H57" s="16" t="n">
-        <v>78</v>
-      </c>
-      <c r="I57" s="16" t="n">
-        <v>706</v>
-      </c>
-      <c r="J57" s="16" t="n">
-        <v>216</v>
-      </c>
-      <c r="K57" s="16" t="n">
-        <v>137</v>
-      </c>
-      <c r="L57" s="16" t="n">
         <v>1960</v>
       </c>
       <c r="N57" s="17">
@@ -11729,33 +10808,6 @@
         </is>
       </c>
       <c r="C58" s="16" t="n">
-        <v>1221</v>
-      </c>
-      <c r="D58" s="16" t="n">
-        <v>305</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>44</v>
-      </c>
-      <c r="F58" s="16" t="n">
-        <v>1264</v>
-      </c>
-      <c r="G58" s="16" t="n">
-        <v>392</v>
-      </c>
-      <c r="H58" s="16" t="n">
-        <v>262</v>
-      </c>
-      <c r="I58" s="16" t="n">
-        <v>610</v>
-      </c>
-      <c r="J58" s="16" t="n">
-        <v>174</v>
-      </c>
-      <c r="K58" s="16" t="n">
-        <v>87</v>
-      </c>
-      <c r="L58" s="16" t="n">
         <v>4359</v>
       </c>
       <c r="N58" s="17">
@@ -11770,33 +10822,6 @@
         </is>
       </c>
       <c r="C59" s="16" t="n">
-        <v>903</v>
-      </c>
-      <c r="D59" s="16" t="n">
-        <v>236</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>43</v>
-      </c>
-      <c r="F59" s="16" t="n">
-        <v>430</v>
-      </c>
-      <c r="G59" s="16" t="n">
-        <v>129</v>
-      </c>
-      <c r="H59" s="16" t="n">
-        <v>86</v>
-      </c>
-      <c r="I59" s="16" t="n">
-        <v>215</v>
-      </c>
-      <c r="J59" s="16" t="n">
-        <v>64</v>
-      </c>
-      <c r="K59" s="16" t="n">
-        <v>43</v>
-      </c>
-      <c r="L59" s="16" t="n">
         <v>2149</v>
       </c>
       <c r="N59" s="17">
@@ -11811,33 +10836,6 @@
         </is>
       </c>
       <c r="C60" s="16" t="n">
-        <v>5635</v>
-      </c>
-      <c r="D60" s="16" t="n">
-        <v>1409</v>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>282</v>
-      </c>
-      <c r="F60" s="16" t="n">
-        <v>10707</v>
-      </c>
-      <c r="G60" s="16" t="n">
-        <v>3099</v>
-      </c>
-      <c r="H60" s="16" t="n">
-        <v>2254</v>
-      </c>
-      <c r="I60" s="16" t="n">
-        <v>3381</v>
-      </c>
-      <c r="J60" s="16" t="n">
-        <v>845</v>
-      </c>
-      <c r="K60" s="16" t="n">
-        <v>564</v>
-      </c>
-      <c r="L60" s="16" t="n">
         <v>28176</v>
       </c>
       <c r="N60" s="17">
@@ -11853,42 +10851,6 @@
       </c>
       <c r="C61" s="18">
         <f>SUM(C19:C60)</f>
-        <v>54790</v>
-      </c>
-      <c r="D61" s="18">
-        <f>SUM(D19:D60)</f>
-        <v>13925</v>
-      </c>
-      <c r="E61" s="18">
-        <f>SUM(E19:E60)</f>
-        <v>2556</v>
-      </c>
-      <c r="F61" s="18">
-        <f>SUM(F19:F60)</f>
-        <v>72141</v>
-      </c>
-      <c r="G61" s="18">
-        <f>SUM(G19:G60)</f>
-        <v>21214</v>
-      </c>
-      <c r="H61" s="18">
-        <f>SUM(H19:H60)</f>
-        <v>15100</v>
-      </c>
-      <c r="I61" s="18">
-        <f>SUM(I19:I60)</f>
-        <v>30647</v>
-      </c>
-      <c r="J61" s="18">
-        <f>SUM(J19:J60)</f>
-        <v>8348</v>
-      </c>
-      <c r="K61" s="18">
-        <f>SUM(K19:K60)</f>
-        <v>5193</v>
-      </c>
-      <c r="L61" s="18">
-        <f>SUM(L19:L60)</f>
         <v>223914</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
@@ -11933,52 +10895,7 @@
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Res edif.</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="inlineStr">
-        <is>
-          <t>Res cont.</t>
-        </is>
-      </c>
-      <c r="E67" s="12" t="inlineStr">
-        <is>
-          <t>Res PB</t>
-        </is>
-      </c>
-      <c r="F67" s="12" t="inlineStr">
-        <is>
-          <t>Com edif.</t>
-        </is>
-      </c>
-      <c r="G67" s="12" t="inlineStr">
-        <is>
-          <t>Com cont.</t>
-        </is>
-      </c>
-      <c r="H67" s="12" t="inlineStr">
-        <is>
-          <t>Com PB</t>
-        </is>
-      </c>
-      <c r="I67" s="12" t="inlineStr">
-        <is>
-          <t>Ind edif.</t>
-        </is>
-      </c>
-      <c r="J67" s="12" t="inlineStr">
-        <is>
-          <t>Ind cont.</t>
-        </is>
-      </c>
-      <c r="K67" s="12" t="inlineStr">
-        <is>
-          <t>Ind PB</t>
-        </is>
-      </c>
-      <c r="L67" s="12" t="inlineStr">
-        <is>
-          <t>Suma</t>
+          <t>Suma asegurada</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -12000,51 +10917,6 @@
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Res Building</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr">
-        <is>
-          <t>Res Content</t>
-        </is>
-      </c>
-      <c r="E68" s="14" t="inlineStr">
-        <is>
-          <t>Res BI</t>
-        </is>
-      </c>
-      <c r="F68" s="14" t="inlineStr">
-        <is>
-          <t>Com Building</t>
-        </is>
-      </c>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>Com Content</t>
-        </is>
-      </c>
-      <c r="H68" s="14" t="inlineStr">
-        <is>
-          <t>Com BI</t>
-        </is>
-      </c>
-      <c r="I68" s="14" t="inlineStr">
-        <is>
-          <t>Ind Building</t>
-        </is>
-      </c>
-      <c r="J68" s="14" t="inlineStr">
-        <is>
-          <t>Ind Content</t>
-        </is>
-      </c>
-      <c r="K68" s="14" t="inlineStr">
-        <is>
-          <t>Ind BI</t>
-        </is>
-      </c>
-      <c r="L68" s="14" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -12061,33 +10933,6 @@
         </is>
       </c>
       <c r="C69" s="16" t="n">
-        <v>553</v>
-      </c>
-      <c r="D69" s="16" t="n">
-        <v>145</v>
-      </c>
-      <c r="E69" s="16" t="n">
-        <v>26</v>
-      </c>
-      <c r="F69" s="16" t="n">
-        <v>263</v>
-      </c>
-      <c r="G69" s="16" t="n">
-        <v>79</v>
-      </c>
-      <c r="H69" s="16" t="n">
-        <v>53</v>
-      </c>
-      <c r="I69" s="16" t="n">
-        <v>132</v>
-      </c>
-      <c r="J69" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="K69" s="16" t="n">
-        <v>26</v>
-      </c>
-      <c r="L69" s="16" t="n">
         <v>1317</v>
       </c>
       <c r="N69" s="17">
@@ -12102,33 +10947,6 @@
         </is>
       </c>
       <c r="C70" s="16" t="n">
-        <v>1062</v>
-      </c>
-      <c r="D70" s="16" t="n">
-        <v>265</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>38</v>
-      </c>
-      <c r="F70" s="16" t="n">
-        <v>1099</v>
-      </c>
-      <c r="G70" s="16" t="n">
-        <v>341</v>
-      </c>
-      <c r="H70" s="16" t="n">
-        <v>227</v>
-      </c>
-      <c r="I70" s="16" t="n">
-        <v>531</v>
-      </c>
-      <c r="J70" s="16" t="n">
-        <v>152</v>
-      </c>
-      <c r="K70" s="16" t="n">
-        <v>76</v>
-      </c>
-      <c r="L70" s="16" t="n">
         <v>3791</v>
       </c>
       <c r="N70" s="17">
@@ -12143,33 +10961,6 @@
         </is>
       </c>
       <c r="C71" s="16" t="n">
-        <v>3401</v>
-      </c>
-      <c r="D71" s="16" t="n">
-        <v>850</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>170</v>
-      </c>
-      <c r="F71" s="16" t="n">
-        <v>6463</v>
-      </c>
-      <c r="G71" s="16" t="n">
-        <v>1871</v>
-      </c>
-      <c r="H71" s="16" t="n">
-        <v>1361</v>
-      </c>
-      <c r="I71" s="16" t="n">
-        <v>2041</v>
-      </c>
-      <c r="J71" s="16" t="n">
-        <v>510</v>
-      </c>
-      <c r="K71" s="16" t="n">
-        <v>340</v>
-      </c>
-      <c r="L71" s="16" t="n">
         <v>17007</v>
       </c>
       <c r="N71" s="17">
@@ -12184,33 +10975,6 @@
         </is>
       </c>
       <c r="C72" s="16" t="n">
-        <v>972</v>
-      </c>
-      <c r="D72" s="16" t="n">
-        <v>255</v>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="F72" s="16" t="n">
-        <v>463</v>
-      </c>
-      <c r="G72" s="16" t="n">
-        <v>139</v>
-      </c>
-      <c r="H72" s="16" t="n">
-        <v>93</v>
-      </c>
-      <c r="I72" s="16" t="n">
-        <v>232</v>
-      </c>
-      <c r="J72" s="16" t="n">
-        <v>69</v>
-      </c>
-      <c r="K72" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="L72" s="16" t="n">
         <v>2315</v>
       </c>
       <c r="N72" s="17">
@@ -12225,33 +10989,6 @@
         </is>
       </c>
       <c r="C73" s="16" t="n">
-        <v>1582</v>
-      </c>
-      <c r="D73" s="16" t="n">
-        <v>395</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="F73" s="16" t="n">
-        <v>1638</v>
-      </c>
-      <c r="G73" s="16" t="n">
-        <v>508</v>
-      </c>
-      <c r="H73" s="16" t="n">
-        <v>339</v>
-      </c>
-      <c r="I73" s="16" t="n">
-        <v>791</v>
-      </c>
-      <c r="J73" s="16" t="n">
-        <v>226</v>
-      </c>
-      <c r="K73" s="16" t="n">
-        <v>113</v>
-      </c>
-      <c r="L73" s="16" t="n">
         <v>5648</v>
       </c>
       <c r="N73" s="17">
@@ -12266,33 +11003,6 @@
         </is>
       </c>
       <c r="C74" s="16" t="n">
-        <v>785</v>
-      </c>
-      <c r="D74" s="16" t="n">
-        <v>206</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>37</v>
-      </c>
-      <c r="F74" s="16" t="n">
-        <v>374</v>
-      </c>
-      <c r="G74" s="16" t="n">
-        <v>112</v>
-      </c>
-      <c r="H74" s="16" t="n">
-        <v>75</v>
-      </c>
-      <c r="I74" s="16" t="n">
-        <v>187</v>
-      </c>
-      <c r="J74" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="K74" s="16" t="n">
-        <v>37</v>
-      </c>
-      <c r="L74" s="16" t="n">
         <v>1869</v>
       </c>
       <c r="N74" s="17">
@@ -12307,33 +11017,6 @@
         </is>
       </c>
       <c r="C75" s="16" t="n">
-        <v>6816</v>
-      </c>
-      <c r="D75" s="16" t="n">
-        <v>1704</v>
-      </c>
-      <c r="E75" s="16" t="n">
-        <v>341</v>
-      </c>
-      <c r="F75" s="16" t="n">
-        <v>12950</v>
-      </c>
-      <c r="G75" s="16" t="n">
-        <v>3749</v>
-      </c>
-      <c r="H75" s="16" t="n">
-        <v>2726</v>
-      </c>
-      <c r="I75" s="16" t="n">
-        <v>4090</v>
-      </c>
-      <c r="J75" s="16" t="n">
-        <v>1022</v>
-      </c>
-      <c r="K75" s="16" t="n">
-        <v>682</v>
-      </c>
-      <c r="L75" s="16" t="n">
         <v>34080</v>
       </c>
       <c r="N75" s="17">
@@ -12348,33 +11031,6 @@
         </is>
       </c>
       <c r="C76" s="16" t="n">
-        <v>685</v>
-      </c>
-      <c r="D76" s="16" t="n">
-        <v>196</v>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="F76" s="16" t="n">
-        <v>881</v>
-      </c>
-      <c r="G76" s="16" t="n">
-        <v>245</v>
-      </c>
-      <c r="H76" s="16" t="n">
-        <v>196</v>
-      </c>
-      <c r="I76" s="16" t="n">
-        <v>1762</v>
-      </c>
-      <c r="J76" s="16" t="n">
-        <v>539</v>
-      </c>
-      <c r="K76" s="16" t="n">
-        <v>343</v>
-      </c>
-      <c r="L76" s="16" t="n">
         <v>4896</v>
       </c>
       <c r="N76" s="17">
@@ -12389,33 +11045,6 @@
         </is>
       </c>
       <c r="C77" s="16" t="n">
-        <v>999</v>
-      </c>
-      <c r="D77" s="16" t="n">
-        <v>262</v>
-      </c>
-      <c r="E77" s="16" t="n">
-        <v>48</v>
-      </c>
-      <c r="F77" s="16" t="n">
-        <v>476</v>
-      </c>
-      <c r="G77" s="16" t="n">
-        <v>143</v>
-      </c>
-      <c r="H77" s="16" t="n">
-        <v>95</v>
-      </c>
-      <c r="I77" s="16" t="n">
-        <v>238</v>
-      </c>
-      <c r="J77" s="16" t="n">
-        <v>71</v>
-      </c>
-      <c r="K77" s="16" t="n">
-        <v>48</v>
-      </c>
-      <c r="L77" s="16" t="n">
         <v>2380</v>
       </c>
       <c r="N77" s="17">
@@ -12430,33 +11059,6 @@
         </is>
       </c>
       <c r="C78" s="16" t="n">
-        <v>2043</v>
-      </c>
-      <c r="D78" s="16" t="n">
-        <v>511</v>
-      </c>
-      <c r="E78" s="16" t="n">
-        <v>73</v>
-      </c>
-      <c r="F78" s="16" t="n">
-        <v>2116</v>
-      </c>
-      <c r="G78" s="16" t="n">
-        <v>657</v>
-      </c>
-      <c r="H78" s="16" t="n">
-        <v>438</v>
-      </c>
-      <c r="I78" s="16" t="n">
-        <v>1021</v>
-      </c>
-      <c r="J78" s="16" t="n">
-        <v>292</v>
-      </c>
-      <c r="K78" s="16" t="n">
-        <v>146</v>
-      </c>
-      <c r="L78" s="16" t="n">
         <v>7297</v>
       </c>
       <c r="N78" s="17">
@@ -12471,33 +11073,6 @@
         </is>
       </c>
       <c r="C79" s="16" t="n">
-        <v>620</v>
-      </c>
-      <c r="D79" s="16" t="n">
-        <v>162</v>
-      </c>
-      <c r="E79" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="F79" s="16" t="n">
-        <v>295</v>
-      </c>
-      <c r="G79" s="16" t="n">
-        <v>89</v>
-      </c>
-      <c r="H79" s="16" t="n">
-        <v>59</v>
-      </c>
-      <c r="I79" s="16" t="n">
-        <v>148</v>
-      </c>
-      <c r="J79" s="16" t="n">
-        <v>44</v>
-      </c>
-      <c r="K79" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="L79" s="16" t="n">
         <v>1477</v>
       </c>
       <c r="N79" s="17">
@@ -12512,33 +11087,6 @@
         </is>
       </c>
       <c r="C80" s="16" t="n">
-        <v>1673</v>
-      </c>
-      <c r="D80" s="16" t="n">
-        <v>418</v>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="F80" s="16" t="n">
-        <v>3179</v>
-      </c>
-      <c r="G80" s="16" t="n">
-        <v>920</v>
-      </c>
-      <c r="H80" s="16" t="n">
-        <v>669</v>
-      </c>
-      <c r="I80" s="16" t="n">
-        <v>1004</v>
-      </c>
-      <c r="J80" s="16" t="n">
-        <v>251</v>
-      </c>
-      <c r="K80" s="16" t="n">
-        <v>167</v>
-      </c>
-      <c r="L80" s="16" t="n">
         <v>8365</v>
       </c>
       <c r="N80" s="17">
@@ -12553,33 +11101,6 @@
         </is>
       </c>
       <c r="C81" s="16" t="n">
-        <v>907</v>
-      </c>
-      <c r="D81" s="16" t="n">
-        <v>227</v>
-      </c>
-      <c r="E81" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="F81" s="16" t="n">
-        <v>939</v>
-      </c>
-      <c r="G81" s="16" t="n">
-        <v>292</v>
-      </c>
-      <c r="H81" s="16" t="n">
-        <v>194</v>
-      </c>
-      <c r="I81" s="16" t="n">
-        <v>453</v>
-      </c>
-      <c r="J81" s="16" t="n">
-        <v>130</v>
-      </c>
-      <c r="K81" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="L81" s="16" t="n">
         <v>3239</v>
       </c>
       <c r="N81" s="17">
@@ -12596,33 +11117,6 @@
       <c r="C82" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D82" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="16" t="n">
-        <v>0</v>
-      </c>
       <c r="N82" s="17">
         <f>ROW()</f>
         <v>82</v>
@@ -12635,33 +11129,6 @@
         </is>
       </c>
       <c r="C83" s="16" t="n">
-        <v>1178</v>
-      </c>
-      <c r="D83" s="16" t="n">
-        <v>308</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="F83" s="16" t="n">
-        <v>561</v>
-      </c>
-      <c r="G83" s="16" t="n">
-        <v>168</v>
-      </c>
-      <c r="H83" s="16" t="n">
-        <v>112</v>
-      </c>
-      <c r="I83" s="16" t="n">
-        <v>280</v>
-      </c>
-      <c r="J83" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="K83" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="L83" s="16" t="n">
         <v>2803</v>
       </c>
       <c r="N83" s="17">
@@ -12676,33 +11143,6 @@
         </is>
       </c>
       <c r="C84" s="16" t="n">
-        <v>1092</v>
-      </c>
-      <c r="D84" s="16" t="n">
-        <v>273</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>55</v>
-      </c>
-      <c r="F84" s="16" t="n">
-        <v>2074</v>
-      </c>
-      <c r="G84" s="16" t="n">
-        <v>600</v>
-      </c>
-      <c r="H84" s="16" t="n">
-        <v>437</v>
-      </c>
-      <c r="I84" s="16" t="n">
-        <v>655</v>
-      </c>
-      <c r="J84" s="16" t="n">
-        <v>164</v>
-      </c>
-      <c r="K84" s="16" t="n">
-        <v>109</v>
-      </c>
-      <c r="L84" s="16" t="n">
         <v>5459</v>
       </c>
       <c r="N84" s="17">
@@ -12717,33 +11157,6 @@
         </is>
       </c>
       <c r="C85" s="16" t="n">
-        <v>271</v>
-      </c>
-      <c r="D85" s="16" t="n">
-        <v>77</v>
-      </c>
-      <c r="E85" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="F85" s="16" t="n">
-        <v>348</v>
-      </c>
-      <c r="G85" s="16" t="n">
-        <v>97</v>
-      </c>
-      <c r="H85" s="16" t="n">
-        <v>77</v>
-      </c>
-      <c r="I85" s="16" t="n">
-        <v>696</v>
-      </c>
-      <c r="J85" s="16" t="n">
-        <v>213</v>
-      </c>
-      <c r="K85" s="16" t="n">
-        <v>135</v>
-      </c>
-      <c r="L85" s="16" t="n">
         <v>1933</v>
       </c>
       <c r="N85" s="17">
@@ -12758,33 +11171,6 @@
         </is>
       </c>
       <c r="C86" s="16" t="n">
-        <v>1178</v>
-      </c>
-      <c r="D86" s="16" t="n">
-        <v>294</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>42</v>
-      </c>
-      <c r="F86" s="16" t="n">
-        <v>1220</v>
-      </c>
-      <c r="G86" s="16" t="n">
-        <v>378</v>
-      </c>
-      <c r="H86" s="16" t="n">
-        <v>252</v>
-      </c>
-      <c r="I86" s="16" t="n">
-        <v>589</v>
-      </c>
-      <c r="J86" s="16" t="n">
-        <v>168</v>
-      </c>
-      <c r="K86" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="L86" s="16" t="n">
         <v>4205</v>
       </c>
       <c r="N86" s="17">
@@ -12799,33 +11185,6 @@
         </is>
       </c>
       <c r="C87" s="16" t="n">
-        <v>4929</v>
-      </c>
-      <c r="D87" s="16" t="n">
-        <v>1232</v>
-      </c>
-      <c r="E87" s="16" t="n">
-        <v>246</v>
-      </c>
-      <c r="F87" s="16" t="n">
-        <v>9366</v>
-      </c>
-      <c r="G87" s="16" t="n">
-        <v>2711</v>
-      </c>
-      <c r="H87" s="16" t="n">
-        <v>1972</v>
-      </c>
-      <c r="I87" s="16" t="n">
-        <v>2958</v>
-      </c>
-      <c r="J87" s="16" t="n">
-        <v>739</v>
-      </c>
-      <c r="K87" s="16" t="n">
-        <v>493</v>
-      </c>
-      <c r="L87" s="16" t="n">
         <v>24646</v>
       </c>
       <c r="N87" s="17">
@@ -12840,33 +11199,6 @@
         </is>
       </c>
       <c r="C88" s="16" t="n">
-        <v>1102</v>
-      </c>
-      <c r="D88" s="16" t="n">
-        <v>289</v>
-      </c>
-      <c r="E88" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="F88" s="16" t="n">
-        <v>525</v>
-      </c>
-      <c r="G88" s="16" t="n">
-        <v>157</v>
-      </c>
-      <c r="H88" s="16" t="n">
-        <v>105</v>
-      </c>
-      <c r="I88" s="16" t="n">
-        <v>262</v>
-      </c>
-      <c r="J88" s="16" t="n">
-        <v>79</v>
-      </c>
-      <c r="K88" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="L88" s="16" t="n">
         <v>2623</v>
       </c>
       <c r="N88" s="17">
@@ -12881,33 +11213,6 @@
         </is>
       </c>
       <c r="C89" s="16" t="n">
-        <v>1876</v>
-      </c>
-      <c r="D89" s="16" t="n">
-        <v>469</v>
-      </c>
-      <c r="E89" s="16" t="n">
-        <v>67</v>
-      </c>
-      <c r="F89" s="16" t="n">
-        <v>1943</v>
-      </c>
-      <c r="G89" s="16" t="n">
-        <v>603</v>
-      </c>
-      <c r="H89" s="16" t="n">
-        <v>402</v>
-      </c>
-      <c r="I89" s="16" t="n">
-        <v>938</v>
-      </c>
-      <c r="J89" s="16" t="n">
-        <v>268</v>
-      </c>
-      <c r="K89" s="16" t="n">
-        <v>134</v>
-      </c>
-      <c r="L89" s="16" t="n">
         <v>6700</v>
       </c>
       <c r="N89" s="17">
@@ -12922,33 +11227,6 @@
         </is>
       </c>
       <c r="C90" s="16" t="n">
-        <v>705</v>
-      </c>
-      <c r="D90" s="16" t="n">
-        <v>185</v>
-      </c>
-      <c r="E90" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="F90" s="16" t="n">
-        <v>336</v>
-      </c>
-      <c r="G90" s="16" t="n">
-        <v>101</v>
-      </c>
-      <c r="H90" s="16" t="n">
-        <v>67</v>
-      </c>
-      <c r="I90" s="16" t="n">
-        <v>168</v>
-      </c>
-      <c r="J90" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="K90" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="L90" s="16" t="n">
         <v>1680</v>
       </c>
       <c r="N90" s="17">
@@ -12963,33 +11241,6 @@
         </is>
       </c>
       <c r="C91" s="16" t="n">
-        <v>629</v>
-      </c>
-      <c r="D91" s="16" t="n">
-        <v>180</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="F91" s="16" t="n">
-        <v>809</v>
-      </c>
-      <c r="G91" s="16" t="n">
-        <v>225</v>
-      </c>
-      <c r="H91" s="16" t="n">
-        <v>180</v>
-      </c>
-      <c r="I91" s="16" t="n">
-        <v>1617</v>
-      </c>
-      <c r="J91" s="16" t="n">
-        <v>494</v>
-      </c>
-      <c r="K91" s="16" t="n">
-        <v>314</v>
-      </c>
-      <c r="L91" s="16" t="n">
         <v>4493</v>
       </c>
       <c r="N91" s="17">
@@ -13004,33 +11255,6 @@
         </is>
       </c>
       <c r="C92" s="16" t="n">
-        <v>614</v>
-      </c>
-      <c r="D92" s="16" t="n">
-        <v>153</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="F92" s="16" t="n">
-        <v>1166</v>
-      </c>
-      <c r="G92" s="16" t="n">
-        <v>338</v>
-      </c>
-      <c r="H92" s="16" t="n">
-        <v>246</v>
-      </c>
-      <c r="I92" s="16" t="n">
-        <v>368</v>
-      </c>
-      <c r="J92" s="16" t="n">
-        <v>92</v>
-      </c>
-      <c r="K92" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="L92" s="16" t="n">
         <v>3069</v>
       </c>
       <c r="N92" s="17">
@@ -13045,33 +11269,6 @@
         </is>
       </c>
       <c r="C93" s="16" t="n">
-        <v>598</v>
-      </c>
-      <c r="D93" s="16" t="n">
-        <v>157</v>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="F93" s="16" t="n">
-        <v>285</v>
-      </c>
-      <c r="G93" s="16" t="n">
-        <v>85</v>
-      </c>
-      <c r="H93" s="16" t="n">
-        <v>57</v>
-      </c>
-      <c r="I93" s="16" t="n">
-        <v>142</v>
-      </c>
-      <c r="J93" s="16" t="n">
-        <v>43</v>
-      </c>
-      <c r="K93" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="L93" s="16" t="n">
         <v>1423</v>
       </c>
       <c r="N93" s="17">
@@ -13086,33 +11283,6 @@
         </is>
       </c>
       <c r="C94" s="16" t="n">
-        <v>1713</v>
-      </c>
-      <c r="D94" s="16" t="n">
-        <v>428</v>
-      </c>
-      <c r="E94" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="F94" s="16" t="n">
-        <v>1774</v>
-      </c>
-      <c r="G94" s="16" t="n">
-        <v>551</v>
-      </c>
-      <c r="H94" s="16" t="n">
-        <v>367</v>
-      </c>
-      <c r="I94" s="16" t="n">
-        <v>856</v>
-      </c>
-      <c r="J94" s="16" t="n">
-        <v>245</v>
-      </c>
-      <c r="K94" s="16" t="n">
-        <v>122</v>
-      </c>
-      <c r="L94" s="16" t="n">
         <v>6117</v>
       </c>
       <c r="N94" s="17">
@@ -13127,33 +11297,6 @@
         </is>
       </c>
       <c r="C95" s="16" t="n">
-        <v>919</v>
-      </c>
-      <c r="D95" s="16" t="n">
-        <v>241</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>44</v>
-      </c>
-      <c r="F95" s="16" t="n">
-        <v>438</v>
-      </c>
-      <c r="G95" s="16" t="n">
-        <v>131</v>
-      </c>
-      <c r="H95" s="16" t="n">
-        <v>88</v>
-      </c>
-      <c r="I95" s="16" t="n">
-        <v>219</v>
-      </c>
-      <c r="J95" s="16" t="n">
-        <v>66</v>
-      </c>
-      <c r="K95" s="16" t="n">
-        <v>44</v>
-      </c>
-      <c r="L95" s="16" t="n">
         <v>2190</v>
       </c>
       <c r="N95" s="17">
@@ -13168,33 +11311,6 @@
         </is>
       </c>
       <c r="C96" s="16" t="n">
-        <v>1807</v>
-      </c>
-      <c r="D96" s="16" t="n">
-        <v>473</v>
-      </c>
-      <c r="E96" s="16" t="n">
-        <v>86</v>
-      </c>
-      <c r="F96" s="16" t="n">
-        <v>861</v>
-      </c>
-      <c r="G96" s="16" t="n">
-        <v>258</v>
-      </c>
-      <c r="H96" s="16" t="n">
-        <v>172</v>
-      </c>
-      <c r="I96" s="16" t="n">
-        <v>430</v>
-      </c>
-      <c r="J96" s="16" t="n">
-        <v>129</v>
-      </c>
-      <c r="K96" s="16" t="n">
-        <v>86</v>
-      </c>
-      <c r="L96" s="16" t="n">
         <v>4302</v>
       </c>
       <c r="N96" s="17">
@@ -13209,33 +11325,6 @@
         </is>
       </c>
       <c r="C97" s="16" t="n">
-        <v>724</v>
-      </c>
-      <c r="D97" s="16" t="n">
-        <v>181</v>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>36</v>
-      </c>
-      <c r="F97" s="16" t="n">
-        <v>1376</v>
-      </c>
-      <c r="G97" s="16" t="n">
-        <v>398</v>
-      </c>
-      <c r="H97" s="16" t="n">
-        <v>290</v>
-      </c>
-      <c r="I97" s="16" t="n">
-        <v>435</v>
-      </c>
-      <c r="J97" s="16" t="n">
-        <v>109</v>
-      </c>
-      <c r="K97" s="16" t="n">
-        <v>72</v>
-      </c>
-      <c r="L97" s="16" t="n">
         <v>3621</v>
       </c>
       <c r="N97" s="17">
@@ -13250,33 +11339,6 @@
         </is>
       </c>
       <c r="C98" s="16" t="n">
-        <v>248</v>
-      </c>
-      <c r="D98" s="16" t="n">
-        <v>71</v>
-      </c>
-      <c r="E98" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="F98" s="16" t="n">
-        <v>319</v>
-      </c>
-      <c r="G98" s="16" t="n">
-        <v>89</v>
-      </c>
-      <c r="H98" s="16" t="n">
-        <v>71</v>
-      </c>
-      <c r="I98" s="16" t="n">
-        <v>638</v>
-      </c>
-      <c r="J98" s="16" t="n">
-        <v>195</v>
-      </c>
-      <c r="K98" s="16" t="n">
-        <v>124</v>
-      </c>
-      <c r="L98" s="16" t="n">
         <v>1773</v>
       </c>
       <c r="N98" s="17">
@@ -13291,33 +11353,6 @@
         </is>
       </c>
       <c r="C99" s="16" t="n">
-        <v>1945</v>
-      </c>
-      <c r="D99" s="16" t="n">
-        <v>486</v>
-      </c>
-      <c r="E99" s="16" t="n">
-        <v>69</v>
-      </c>
-      <c r="F99" s="16" t="n">
-        <v>2014</v>
-      </c>
-      <c r="G99" s="16" t="n">
-        <v>625</v>
-      </c>
-      <c r="H99" s="16" t="n">
-        <v>417</v>
-      </c>
-      <c r="I99" s="16" t="n">
-        <v>972</v>
-      </c>
-      <c r="J99" s="16" t="n">
-        <v>278</v>
-      </c>
-      <c r="K99" s="16" t="n">
-        <v>139</v>
-      </c>
-      <c r="L99" s="16" t="n">
         <v>6945</v>
       </c>
       <c r="N99" s="17">
@@ -13332,33 +11367,6 @@
         </is>
       </c>
       <c r="C100" s="16" t="n">
-        <v>1035</v>
-      </c>
-      <c r="D100" s="16" t="n">
-        <v>271</v>
-      </c>
-      <c r="E100" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="F100" s="16" t="n">
-        <v>493</v>
-      </c>
-      <c r="G100" s="16" t="n">
-        <v>148</v>
-      </c>
-      <c r="H100" s="16" t="n">
-        <v>99</v>
-      </c>
-      <c r="I100" s="16" t="n">
-        <v>246</v>
-      </c>
-      <c r="J100" s="16" t="n">
-        <v>74</v>
-      </c>
-      <c r="K100" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="L100" s="16" t="n">
         <v>2464</v>
       </c>
       <c r="N100" s="17">
@@ -13373,33 +11381,6 @@
         </is>
       </c>
       <c r="C101" s="16" t="n">
-        <v>1039</v>
-      </c>
-      <c r="D101" s="16" t="n">
-        <v>260</v>
-      </c>
-      <c r="E101" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="F101" s="16" t="n">
-        <v>1973</v>
-      </c>
-      <c r="G101" s="16" t="n">
-        <v>571</v>
-      </c>
-      <c r="H101" s="16" t="n">
-        <v>415</v>
-      </c>
-      <c r="I101" s="16" t="n">
-        <v>623</v>
-      </c>
-      <c r="J101" s="16" t="n">
-        <v>156</v>
-      </c>
-      <c r="K101" s="16" t="n">
-        <v>104</v>
-      </c>
-      <c r="L101" s="16" t="n">
         <v>5193</v>
       </c>
       <c r="N101" s="17">
@@ -13414,33 +11395,6 @@
         </is>
       </c>
       <c r="C102" s="16" t="n">
-        <v>647</v>
-      </c>
-      <c r="D102" s="16" t="n">
-        <v>169</v>
-      </c>
-      <c r="E102" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="F102" s="16" t="n">
-        <v>308</v>
-      </c>
-      <c r="G102" s="16" t="n">
-        <v>92</v>
-      </c>
-      <c r="H102" s="16" t="n">
-        <v>62</v>
-      </c>
-      <c r="I102" s="16" t="n">
-        <v>154</v>
-      </c>
-      <c r="J102" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="K102" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="L102" s="16" t="n">
         <v>1540</v>
       </c>
       <c r="N102" s="17">
@@ -13455,33 +11409,6 @@
         </is>
       </c>
       <c r="C103" s="16" t="n">
-        <v>946</v>
-      </c>
-      <c r="D103" s="16" t="n">
-        <v>236</v>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="F103" s="16" t="n">
-        <v>979</v>
-      </c>
-      <c r="G103" s="16" t="n">
-        <v>304</v>
-      </c>
-      <c r="H103" s="16" t="n">
-        <v>203</v>
-      </c>
-      <c r="I103" s="16" t="n">
-        <v>473</v>
-      </c>
-      <c r="J103" s="16" t="n">
-        <v>135</v>
-      </c>
-      <c r="K103" s="16" t="n">
-        <v>68</v>
-      </c>
-      <c r="L103" s="16" t="n">
         <v>3378</v>
       </c>
       <c r="N103" s="17">
@@ -13498,33 +11425,6 @@
       <c r="C104" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="16" t="n">
-        <v>0</v>
-      </c>
       <c r="N104" s="17">
         <f>ROW()</f>
         <v>104</v>
@@ -13537,33 +11437,6 @@
         </is>
       </c>
       <c r="C105" s="16" t="n">
-        <v>1153</v>
-      </c>
-      <c r="D105" s="16" t="n">
-        <v>288</v>
-      </c>
-      <c r="E105" s="16" t="n">
-        <v>58</v>
-      </c>
-      <c r="F105" s="16" t="n">
-        <v>2191</v>
-      </c>
-      <c r="G105" s="16" t="n">
-        <v>634</v>
-      </c>
-      <c r="H105" s="16" t="n">
-        <v>461</v>
-      </c>
-      <c r="I105" s="16" t="n">
-        <v>692</v>
-      </c>
-      <c r="J105" s="16" t="n">
-        <v>173</v>
-      </c>
-      <c r="K105" s="16" t="n">
-        <v>115</v>
-      </c>
-      <c r="L105" s="16" t="n">
         <v>5765</v>
       </c>
       <c r="N105" s="17">
@@ -13578,33 +11451,6 @@
         </is>
       </c>
       <c r="C106" s="16" t="n">
-        <v>1209</v>
-      </c>
-      <c r="D106" s="16" t="n">
-        <v>317</v>
-      </c>
-      <c r="E106" s="16" t="n">
-        <v>58</v>
-      </c>
-      <c r="F106" s="16" t="n">
-        <v>576</v>
-      </c>
-      <c r="G106" s="16" t="n">
-        <v>173</v>
-      </c>
-      <c r="H106" s="16" t="n">
-        <v>115</v>
-      </c>
-      <c r="I106" s="16" t="n">
-        <v>288</v>
-      </c>
-      <c r="J106" s="16" t="n">
-        <v>86</v>
-      </c>
-      <c r="K106" s="16" t="n">
-        <v>58</v>
-      </c>
-      <c r="L106" s="16" t="n">
         <v>2880</v>
       </c>
       <c r="N106" s="17">
@@ -13619,33 +11465,6 @@
         </is>
       </c>
       <c r="C107" s="16" t="n">
-        <v>291</v>
-      </c>
-      <c r="D107" s="16" t="n">
-        <v>83</v>
-      </c>
-      <c r="E107" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="F107" s="16" t="n">
-        <v>375</v>
-      </c>
-      <c r="G107" s="16" t="n">
-        <v>104</v>
-      </c>
-      <c r="H107" s="16" t="n">
-        <v>83</v>
-      </c>
-      <c r="I107" s="16" t="n">
-        <v>749</v>
-      </c>
-      <c r="J107" s="16" t="n">
-        <v>229</v>
-      </c>
-      <c r="K107" s="16" t="n">
-        <v>146</v>
-      </c>
-      <c r="L107" s="16" t="n">
         <v>2081</v>
       </c>
       <c r="N107" s="17">
@@ -13660,33 +11479,6 @@
         </is>
       </c>
       <c r="C108" s="16" t="n">
-        <v>1296</v>
-      </c>
-      <c r="D108" s="16" t="n">
-        <v>324</v>
-      </c>
-      <c r="E108" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="F108" s="16" t="n">
-        <v>1343</v>
-      </c>
-      <c r="G108" s="16" t="n">
-        <v>417</v>
-      </c>
-      <c r="H108" s="16" t="n">
-        <v>278</v>
-      </c>
-      <c r="I108" s="16" t="n">
-        <v>648</v>
-      </c>
-      <c r="J108" s="16" t="n">
-        <v>185</v>
-      </c>
-      <c r="K108" s="16" t="n">
-        <v>93</v>
-      </c>
-      <c r="L108" s="16" t="n">
         <v>4630</v>
       </c>
       <c r="N108" s="17">
@@ -13701,33 +11493,6 @@
         </is>
       </c>
       <c r="C109" s="16" t="n">
-        <v>959</v>
-      </c>
-      <c r="D109" s="16" t="n">
-        <v>251</v>
-      </c>
-      <c r="E109" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="F109" s="16" t="n">
-        <v>457</v>
-      </c>
-      <c r="G109" s="16" t="n">
-        <v>137</v>
-      </c>
-      <c r="H109" s="16" t="n">
-        <v>91</v>
-      </c>
-      <c r="I109" s="16" t="n">
-        <v>228</v>
-      </c>
-      <c r="J109" s="16" t="n">
-        <v>68</v>
-      </c>
-      <c r="K109" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="L109" s="16" t="n">
         <v>2283</v>
       </c>
       <c r="N109" s="17">
@@ -13742,33 +11507,6 @@
         </is>
       </c>
       <c r="C110" s="16" t="n">
-        <v>5985</v>
-      </c>
-      <c r="D110" s="16" t="n">
-        <v>1496</v>
-      </c>
-      <c r="E110" s="16" t="n">
-        <v>299</v>
-      </c>
-      <c r="F110" s="16" t="n">
-        <v>11371</v>
-      </c>
-      <c r="G110" s="16" t="n">
-        <v>3292</v>
-      </c>
-      <c r="H110" s="16" t="n">
-        <v>2394</v>
-      </c>
-      <c r="I110" s="16" t="n">
-        <v>3591</v>
-      </c>
-      <c r="J110" s="16" t="n">
-        <v>898</v>
-      </c>
-      <c r="K110" s="16" t="n">
-        <v>598</v>
-      </c>
-      <c r="L110" s="16" t="n">
         <v>29924</v>
       </c>
       <c r="N110" s="17">
@@ -13784,42 +11522,6 @@
       </c>
       <c r="C111" s="18">
         <f>SUM(C69:C110)</f>
-        <v>58186</v>
-      </c>
-      <c r="D111" s="18">
-        <f>SUM(D69:D110)</f>
-        <v>14788</v>
-      </c>
-      <c r="E111" s="18">
-        <f>SUM(E69:E110)</f>
-        <v>2713</v>
-      </c>
-      <c r="F111" s="18">
-        <f>SUM(F69:F110)</f>
-        <v>76617</v>
-      </c>
-      <c r="G111" s="18">
-        <f>SUM(G69:G110)</f>
-        <v>22532</v>
-      </c>
-      <c r="H111" s="18">
-        <f>SUM(H69:H110)</f>
-        <v>16038</v>
-      </c>
-      <c r="I111" s="18">
-        <f>SUM(I69:I110)</f>
-        <v>32545</v>
-      </c>
-      <c r="J111" s="18">
-        <f>SUM(J69:J110)</f>
-        <v>8868</v>
-      </c>
-      <c r="K111" s="18">
-        <f>SUM(K69:K110)</f>
-        <v>5514</v>
-      </c>
-      <c r="L111" s="18">
-        <f>SUM(L69:L110)</f>
         <v>237801</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
@@ -13864,52 +11566,7 @@
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Res edif.</t>
-        </is>
-      </c>
-      <c r="D117" s="12" t="inlineStr">
-        <is>
-          <t>Res cont.</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>Res PB</t>
-        </is>
-      </c>
-      <c r="F117" s="12" t="inlineStr">
-        <is>
-          <t>Com edif.</t>
-        </is>
-      </c>
-      <c r="G117" s="12" t="inlineStr">
-        <is>
-          <t>Com cont.</t>
-        </is>
-      </c>
-      <c r="H117" s="12" t="inlineStr">
-        <is>
-          <t>Com PB</t>
-        </is>
-      </c>
-      <c r="I117" s="12" t="inlineStr">
-        <is>
-          <t>Ind edif.</t>
-        </is>
-      </c>
-      <c r="J117" s="12" t="inlineStr">
-        <is>
-          <t>Ind cont.</t>
-        </is>
-      </c>
-      <c r="K117" s="12" t="inlineStr">
-        <is>
-          <t>Ind PB</t>
-        </is>
-      </c>
-      <c r="L117" s="12" t="inlineStr">
-        <is>
-          <t>Suma</t>
+          <t>Suma asegurada</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
@@ -13931,51 +11588,6 @@
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>Res Building</t>
-        </is>
-      </c>
-      <c r="D118" s="14" t="inlineStr">
-        <is>
-          <t>Res Content</t>
-        </is>
-      </c>
-      <c r="E118" s="14" t="inlineStr">
-        <is>
-          <t>Res BI</t>
-        </is>
-      </c>
-      <c r="F118" s="14" t="inlineStr">
-        <is>
-          <t>Com Building</t>
-        </is>
-      </c>
-      <c r="G118" s="14" t="inlineStr">
-        <is>
-          <t>Com Content</t>
-        </is>
-      </c>
-      <c r="H118" s="14" t="inlineStr">
-        <is>
-          <t>Com BI</t>
-        </is>
-      </c>
-      <c r="I118" s="14" t="inlineStr">
-        <is>
-          <t>Ind Building</t>
-        </is>
-      </c>
-      <c r="J118" s="14" t="inlineStr">
-        <is>
-          <t>Ind Content</t>
-        </is>
-      </c>
-      <c r="K118" s="14" t="inlineStr">
-        <is>
-          <t>Ind BI</t>
-        </is>
-      </c>
-      <c r="L118" s="14" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -13992,33 +11604,6 @@
         </is>
       </c>
       <c r="C119" s="16" t="n">
-        <v>587</v>
-      </c>
-      <c r="D119" s="16" t="n">
-        <v>154</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="F119" s="16" t="n">
-        <v>280</v>
-      </c>
-      <c r="G119" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="H119" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="I119" s="16" t="n">
-        <v>140</v>
-      </c>
-      <c r="J119" s="16" t="n">
-        <v>42</v>
-      </c>
-      <c r="K119" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="L119" s="16" t="n">
         <v>1399</v>
       </c>
       <c r="N119" s="17">
@@ -14033,33 +11618,6 @@
         </is>
       </c>
       <c r="C120" s="16" t="n">
-        <v>1128</v>
-      </c>
-      <c r="D120" s="16" t="n">
-        <v>282</v>
-      </c>
-      <c r="E120" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="F120" s="16" t="n">
-        <v>1168</v>
-      </c>
-      <c r="G120" s="16" t="n">
-        <v>362</v>
-      </c>
-      <c r="H120" s="16" t="n">
-        <v>242</v>
-      </c>
-      <c r="I120" s="16" t="n">
-        <v>564</v>
-      </c>
-      <c r="J120" s="16" t="n">
-        <v>161</v>
-      </c>
-      <c r="K120" s="16" t="n">
-        <v>81</v>
-      </c>
-      <c r="L120" s="16" t="n">
         <v>4028</v>
       </c>
       <c r="N120" s="17">
@@ -14074,33 +11632,6 @@
         </is>
       </c>
       <c r="C121" s="16" t="n">
-        <v>3613</v>
-      </c>
-      <c r="D121" s="16" t="n">
-        <v>903</v>
-      </c>
-      <c r="E121" s="16" t="n">
-        <v>181</v>
-      </c>
-      <c r="F121" s="16" t="n">
-        <v>6864</v>
-      </c>
-      <c r="G121" s="16" t="n">
-        <v>1987</v>
-      </c>
-      <c r="H121" s="16" t="n">
-        <v>1445</v>
-      </c>
-      <c r="I121" s="16" t="n">
-        <v>2168</v>
-      </c>
-      <c r="J121" s="16" t="n">
-        <v>542</v>
-      </c>
-      <c r="K121" s="16" t="n">
-        <v>361</v>
-      </c>
-      <c r="L121" s="16" t="n">
         <v>18064</v>
       </c>
       <c r="N121" s="17">
@@ -14115,33 +11646,6 @@
         </is>
       </c>
       <c r="C122" s="16" t="n">
-        <v>1033</v>
-      </c>
-      <c r="D122" s="16" t="n">
-        <v>270</v>
-      </c>
-      <c r="E122" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="F122" s="16" t="n">
-        <v>492</v>
-      </c>
-      <c r="G122" s="16" t="n">
-        <v>148</v>
-      </c>
-      <c r="H122" s="16" t="n">
-        <v>98</v>
-      </c>
-      <c r="I122" s="16" t="n">
-        <v>246</v>
-      </c>
-      <c r="J122" s="16" t="n">
-        <v>74</v>
-      </c>
-      <c r="K122" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="L122" s="16" t="n">
         <v>2459</v>
       </c>
       <c r="N122" s="17">
@@ -14156,33 +11660,6 @@
         </is>
       </c>
       <c r="C123" s="16" t="n">
-        <v>1680</v>
-      </c>
-      <c r="D123" s="16" t="n">
-        <v>420</v>
-      </c>
-      <c r="E123" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F123" s="16" t="n">
-        <v>1740</v>
-      </c>
-      <c r="G123" s="16" t="n">
-        <v>540</v>
-      </c>
-      <c r="H123" s="16" t="n">
-        <v>360</v>
-      </c>
-      <c r="I123" s="16" t="n">
-        <v>840</v>
-      </c>
-      <c r="J123" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="K123" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="L123" s="16" t="n">
         <v>6000</v>
       </c>
       <c r="N123" s="17">
@@ -14197,33 +11674,6 @@
         </is>
       </c>
       <c r="C124" s="16" t="n">
-        <v>834</v>
-      </c>
-      <c r="D124" s="16" t="n">
-        <v>218</v>
-      </c>
-      <c r="E124" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="F124" s="16" t="n">
-        <v>397</v>
-      </c>
-      <c r="G124" s="16" t="n">
-        <v>119</v>
-      </c>
-      <c r="H124" s="16" t="n">
-        <v>79</v>
-      </c>
-      <c r="I124" s="16" t="n">
-        <v>199</v>
-      </c>
-      <c r="J124" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="K124" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="L124" s="16" t="n">
         <v>1986</v>
       </c>
       <c r="N124" s="17">
@@ -14238,33 +11688,6 @@
         </is>
       </c>
       <c r="C125" s="16" t="n">
-        <v>7240</v>
-      </c>
-      <c r="D125" s="16" t="n">
-        <v>1810</v>
-      </c>
-      <c r="E125" s="16" t="n">
-        <v>362</v>
-      </c>
-      <c r="F125" s="16" t="n">
-        <v>13755</v>
-      </c>
-      <c r="G125" s="16" t="n">
-        <v>3982</v>
-      </c>
-      <c r="H125" s="16" t="n">
-        <v>2896</v>
-      </c>
-      <c r="I125" s="16" t="n">
-        <v>4344</v>
-      </c>
-      <c r="J125" s="16" t="n">
-        <v>1086</v>
-      </c>
-      <c r="K125" s="16" t="n">
-        <v>724</v>
-      </c>
-      <c r="L125" s="16" t="n">
         <v>36199</v>
       </c>
       <c r="N125" s="17">
@@ -14279,33 +11702,6 @@
         </is>
       </c>
       <c r="C126" s="16" t="n">
-        <v>728</v>
-      </c>
-      <c r="D126" s="16" t="n">
-        <v>208</v>
-      </c>
-      <c r="E126" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="F126" s="16" t="n">
-        <v>936</v>
-      </c>
-      <c r="G126" s="16" t="n">
-        <v>260</v>
-      </c>
-      <c r="H126" s="16" t="n">
-        <v>208</v>
-      </c>
-      <c r="I126" s="16" t="n">
-        <v>1872</v>
-      </c>
-      <c r="J126" s="16" t="n">
-        <v>572</v>
-      </c>
-      <c r="K126" s="16" t="n">
-        <v>364</v>
-      </c>
-      <c r="L126" s="16" t="n">
         <v>5200</v>
       </c>
       <c r="N126" s="17">
@@ -14320,33 +11716,6 @@
         </is>
       </c>
       <c r="C127" s="16" t="n">
-        <v>1061</v>
-      </c>
-      <c r="D127" s="16" t="n">
-        <v>278</v>
-      </c>
-      <c r="E127" s="16" t="n">
-        <v>51</v>
-      </c>
-      <c r="F127" s="16" t="n">
-        <v>505</v>
-      </c>
-      <c r="G127" s="16" t="n">
-        <v>152</v>
-      </c>
-      <c r="H127" s="16" t="n">
-        <v>101</v>
-      </c>
-      <c r="I127" s="16" t="n">
-        <v>253</v>
-      </c>
-      <c r="J127" s="16" t="n">
-        <v>76</v>
-      </c>
-      <c r="K127" s="16" t="n">
-        <v>51</v>
-      </c>
-      <c r="L127" s="16" t="n">
         <v>2528</v>
       </c>
       <c r="N127" s="17">
@@ -14361,33 +11730,6 @@
         </is>
       </c>
       <c r="C128" s="16" t="n">
-        <v>2170</v>
-      </c>
-      <c r="D128" s="16" t="n">
-        <v>542</v>
-      </c>
-      <c r="E128" s="16" t="n">
-        <v>77</v>
-      </c>
-      <c r="F128" s="16" t="n">
-        <v>2247</v>
-      </c>
-      <c r="G128" s="16" t="n">
-        <v>697</v>
-      </c>
-      <c r="H128" s="16" t="n">
-        <v>465</v>
-      </c>
-      <c r="I128" s="16" t="n">
-        <v>1085</v>
-      </c>
-      <c r="J128" s="16" t="n">
-        <v>310</v>
-      </c>
-      <c r="K128" s="16" t="n">
-        <v>155</v>
-      </c>
-      <c r="L128" s="16" t="n">
         <v>7748</v>
       </c>
       <c r="N128" s="17">
@@ -14402,33 +11744,6 @@
         </is>
       </c>
       <c r="C129" s="16" t="n">
-        <v>659</v>
-      </c>
-      <c r="D129" s="16" t="n">
-        <v>172</v>
-      </c>
-      <c r="E129" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="F129" s="16" t="n">
-        <v>314</v>
-      </c>
-      <c r="G129" s="16" t="n">
-        <v>94</v>
-      </c>
-      <c r="H129" s="16" t="n">
-        <v>63</v>
-      </c>
-      <c r="I129" s="16" t="n">
-        <v>157</v>
-      </c>
-      <c r="J129" s="16" t="n">
-        <v>47</v>
-      </c>
-      <c r="K129" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="L129" s="16" t="n">
         <v>1568</v>
       </c>
       <c r="N129" s="17">
@@ -14443,33 +11758,6 @@
         </is>
       </c>
       <c r="C130" s="16" t="n">
-        <v>1777</v>
-      </c>
-      <c r="D130" s="16" t="n">
-        <v>444</v>
-      </c>
-      <c r="E130" s="16" t="n">
-        <v>89</v>
-      </c>
-      <c r="F130" s="16" t="n">
-        <v>3377</v>
-      </c>
-      <c r="G130" s="16" t="n">
-        <v>978</v>
-      </c>
-      <c r="H130" s="16" t="n">
-        <v>711</v>
-      </c>
-      <c r="I130" s="16" t="n">
-        <v>1066</v>
-      </c>
-      <c r="J130" s="16" t="n">
-        <v>267</v>
-      </c>
-      <c r="K130" s="16" t="n">
-        <v>178</v>
-      </c>
-      <c r="L130" s="16" t="n">
         <v>8887</v>
       </c>
       <c r="N130" s="17">
@@ -14484,33 +11772,6 @@
         </is>
       </c>
       <c r="C131" s="16" t="n">
-        <v>963</v>
-      </c>
-      <c r="D131" s="16" t="n">
-        <v>241</v>
-      </c>
-      <c r="E131" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="F131" s="16" t="n">
-        <v>998</v>
-      </c>
-      <c r="G131" s="16" t="n">
-        <v>310</v>
-      </c>
-      <c r="H131" s="16" t="n">
-        <v>206</v>
-      </c>
-      <c r="I131" s="16" t="n">
-        <v>482</v>
-      </c>
-      <c r="J131" s="16" t="n">
-        <v>138</v>
-      </c>
-      <c r="K131" s="16" t="n">
-        <v>69</v>
-      </c>
-      <c r="L131" s="16" t="n">
         <v>3441</v>
       </c>
       <c r="N131" s="17">
@@ -14527,33 +11788,6 @@
       <c r="C132" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="16" t="n">
-        <v>0</v>
-      </c>
       <c r="N132" s="17">
         <f>ROW()</f>
         <v>132</v>
@@ -14566,33 +11800,6 @@
         </is>
       </c>
       <c r="C133" s="16" t="n">
-        <v>1251</v>
-      </c>
-      <c r="D133" s="16" t="n">
-        <v>328</v>
-      </c>
-      <c r="E133" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F133" s="16" t="n">
-        <v>596</v>
-      </c>
-      <c r="G133" s="16" t="n">
-        <v>179</v>
-      </c>
-      <c r="H133" s="16" t="n">
-        <v>119</v>
-      </c>
-      <c r="I133" s="16" t="n">
-        <v>298</v>
-      </c>
-      <c r="J133" s="16" t="n">
-        <v>89</v>
-      </c>
-      <c r="K133" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="L133" s="16" t="n">
         <v>2980</v>
       </c>
       <c r="N133" s="17">
@@ -14607,33 +11814,6 @@
         </is>
       </c>
       <c r="C134" s="16" t="n">
-        <v>1160</v>
-      </c>
-      <c r="D134" s="16" t="n">
-        <v>290</v>
-      </c>
-      <c r="E134" s="16" t="n">
-        <v>58</v>
-      </c>
-      <c r="F134" s="16" t="n">
-        <v>2203</v>
-      </c>
-      <c r="G134" s="16" t="n">
-        <v>638</v>
-      </c>
-      <c r="H134" s="16" t="n">
-        <v>464</v>
-      </c>
-      <c r="I134" s="16" t="n">
-        <v>696</v>
-      </c>
-      <c r="J134" s="16" t="n">
-        <v>174</v>
-      </c>
-      <c r="K134" s="16" t="n">
-        <v>116</v>
-      </c>
-      <c r="L134" s="16" t="n">
         <v>5799</v>
       </c>
       <c r="N134" s="17">
@@ -14648,33 +11828,6 @@
         </is>
       </c>
       <c r="C135" s="16" t="n">
-        <v>287</v>
-      </c>
-      <c r="D135" s="16" t="n">
-        <v>82</v>
-      </c>
-      <c r="E135" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="F135" s="16" t="n">
-        <v>370</v>
-      </c>
-      <c r="G135" s="16" t="n">
-        <v>103</v>
-      </c>
-      <c r="H135" s="16" t="n">
-        <v>82</v>
-      </c>
-      <c r="I135" s="16" t="n">
-        <v>739</v>
-      </c>
-      <c r="J135" s="16" t="n">
-        <v>226</v>
-      </c>
-      <c r="K135" s="16" t="n">
-        <v>144</v>
-      </c>
-      <c r="L135" s="16" t="n">
         <v>2054</v>
       </c>
       <c r="N135" s="17">
@@ -14689,33 +11842,6 @@
         </is>
       </c>
       <c r="C136" s="16" t="n">
-        <v>1251</v>
-      </c>
-      <c r="D136" s="16" t="n">
-        <v>313</v>
-      </c>
-      <c r="E136" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="F136" s="16" t="n">
-        <v>1295</v>
-      </c>
-      <c r="G136" s="16" t="n">
-        <v>402</v>
-      </c>
-      <c r="H136" s="16" t="n">
-        <v>268</v>
-      </c>
-      <c r="I136" s="16" t="n">
-        <v>625</v>
-      </c>
-      <c r="J136" s="16" t="n">
-        <v>179</v>
-      </c>
-      <c r="K136" s="16" t="n">
-        <v>89</v>
-      </c>
-      <c r="L136" s="16" t="n">
         <v>4467</v>
       </c>
       <c r="N136" s="17">
@@ -14730,33 +11856,6 @@
         </is>
       </c>
       <c r="C137" s="16" t="n">
-        <v>5236</v>
-      </c>
-      <c r="D137" s="16" t="n">
-        <v>1309</v>
-      </c>
-      <c r="E137" s="16" t="n">
-        <v>262</v>
-      </c>
-      <c r="F137" s="16" t="n">
-        <v>9948</v>
-      </c>
-      <c r="G137" s="16" t="n">
-        <v>2880</v>
-      </c>
-      <c r="H137" s="16" t="n">
-        <v>2094</v>
-      </c>
-      <c r="I137" s="16" t="n">
-        <v>3141</v>
-      </c>
-      <c r="J137" s="16" t="n">
-        <v>785</v>
-      </c>
-      <c r="K137" s="16" t="n">
-        <v>524</v>
-      </c>
-      <c r="L137" s="16" t="n">
         <v>26179</v>
       </c>
       <c r="N137" s="17">
@@ -14771,33 +11870,6 @@
         </is>
       </c>
       <c r="C138" s="16" t="n">
-        <v>1170</v>
-      </c>
-      <c r="D138" s="16" t="n">
-        <v>306</v>
-      </c>
-      <c r="E138" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="F138" s="16" t="n">
-        <v>557</v>
-      </c>
-      <c r="G138" s="16" t="n">
-        <v>167</v>
-      </c>
-      <c r="H138" s="16" t="n">
-        <v>111</v>
-      </c>
-      <c r="I138" s="16" t="n">
-        <v>279</v>
-      </c>
-      <c r="J138" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="K138" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="L138" s="16" t="n">
         <v>2786</v>
       </c>
       <c r="N138" s="17">
@@ -14812,33 +11884,6 @@
         </is>
       </c>
       <c r="C139" s="16" t="n">
-        <v>1993</v>
-      </c>
-      <c r="D139" s="16" t="n">
-        <v>498</v>
-      </c>
-      <c r="E139" s="16" t="n">
-        <v>71</v>
-      </c>
-      <c r="F139" s="16" t="n">
-        <v>2064</v>
-      </c>
-      <c r="G139" s="16" t="n">
-        <v>641</v>
-      </c>
-      <c r="H139" s="16" t="n">
-        <v>427</v>
-      </c>
-      <c r="I139" s="16" t="n">
-        <v>996</v>
-      </c>
-      <c r="J139" s="16" t="n">
-        <v>285</v>
-      </c>
-      <c r="K139" s="16" t="n">
-        <v>142</v>
-      </c>
-      <c r="L139" s="16" t="n">
         <v>7117</v>
       </c>
       <c r="N139" s="17">
@@ -14853,33 +11898,6 @@
         </is>
       </c>
       <c r="C140" s="16" t="n">
-        <v>749</v>
-      </c>
-      <c r="D140" s="16" t="n">
-        <v>196</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>36</v>
-      </c>
-      <c r="F140" s="16" t="n">
-        <v>356</v>
-      </c>
-      <c r="G140" s="16" t="n">
-        <v>107</v>
-      </c>
-      <c r="H140" s="16" t="n">
-        <v>71</v>
-      </c>
-      <c r="I140" s="16" t="n">
-        <v>178</v>
-      </c>
-      <c r="J140" s="16" t="n">
-        <v>53</v>
-      </c>
-      <c r="K140" s="16" t="n">
-        <v>36</v>
-      </c>
-      <c r="L140" s="16" t="n">
         <v>1782</v>
       </c>
       <c r="N140" s="17">
@@ -14894,33 +11912,6 @@
         </is>
       </c>
       <c r="C141" s="16" t="n">
-        <v>668</v>
-      </c>
-      <c r="D141" s="16" t="n">
-        <v>191</v>
-      </c>
-      <c r="E141" s="16" t="n">
-        <v>48</v>
-      </c>
-      <c r="F141" s="16" t="n">
-        <v>859</v>
-      </c>
-      <c r="G141" s="16" t="n">
-        <v>239</v>
-      </c>
-      <c r="H141" s="16" t="n">
-        <v>191</v>
-      </c>
-      <c r="I141" s="16" t="n">
-        <v>1718</v>
-      </c>
-      <c r="J141" s="16" t="n">
-        <v>525</v>
-      </c>
-      <c r="K141" s="16" t="n">
-        <v>334</v>
-      </c>
-      <c r="L141" s="16" t="n">
         <v>4773</v>
       </c>
       <c r="N141" s="17">
@@ -14935,33 +11926,6 @@
         </is>
       </c>
       <c r="C142" s="16" t="n">
-        <v>652</v>
-      </c>
-      <c r="D142" s="16" t="n">
-        <v>163</v>
-      </c>
-      <c r="E142" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="F142" s="16" t="n">
-        <v>1239</v>
-      </c>
-      <c r="G142" s="16" t="n">
-        <v>359</v>
-      </c>
-      <c r="H142" s="16" t="n">
-        <v>261</v>
-      </c>
-      <c r="I142" s="16" t="n">
-        <v>391</v>
-      </c>
-      <c r="J142" s="16" t="n">
-        <v>98</v>
-      </c>
-      <c r="K142" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="L142" s="16" t="n">
         <v>3261</v>
       </c>
       <c r="N142" s="17">
@@ -14976,33 +11940,6 @@
         </is>
       </c>
       <c r="C143" s="16" t="n">
-        <v>635</v>
-      </c>
-      <c r="D143" s="16" t="n">
-        <v>166</v>
-      </c>
-      <c r="E143" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="F143" s="16" t="n">
-        <v>302</v>
-      </c>
-      <c r="G143" s="16" t="n">
-        <v>91</v>
-      </c>
-      <c r="H143" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="I143" s="16" t="n">
-        <v>151</v>
-      </c>
-      <c r="J143" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="K143" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="L143" s="16" t="n">
         <v>1510</v>
       </c>
       <c r="N143" s="17">
@@ -15017,33 +11954,6 @@
         </is>
       </c>
       <c r="C144" s="16" t="n">
-        <v>1819</v>
-      </c>
-      <c r="D144" s="16" t="n">
-        <v>455</v>
-      </c>
-      <c r="E144" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="F144" s="16" t="n">
-        <v>1884</v>
-      </c>
-      <c r="G144" s="16" t="n">
-        <v>585</v>
-      </c>
-      <c r="H144" s="16" t="n">
-        <v>390</v>
-      </c>
-      <c r="I144" s="16" t="n">
-        <v>910</v>
-      </c>
-      <c r="J144" s="16" t="n">
-        <v>260</v>
-      </c>
-      <c r="K144" s="16" t="n">
-        <v>130</v>
-      </c>
-      <c r="L144" s="16" t="n">
         <v>6498</v>
       </c>
       <c r="N144" s="17">
@@ -15058,33 +11968,6 @@
         </is>
       </c>
       <c r="C145" s="16" t="n">
-        <v>976</v>
-      </c>
-      <c r="D145" s="16" t="n">
-        <v>256</v>
-      </c>
-      <c r="E145" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="F145" s="16" t="n">
-        <v>465</v>
-      </c>
-      <c r="G145" s="16" t="n">
-        <v>139</v>
-      </c>
-      <c r="H145" s="16" t="n">
-        <v>93</v>
-      </c>
-      <c r="I145" s="16" t="n">
-        <v>232</v>
-      </c>
-      <c r="J145" s="16" t="n">
-        <v>70</v>
-      </c>
-      <c r="K145" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="L145" s="16" t="n">
         <v>2323</v>
       </c>
       <c r="N145" s="17">
@@ -15099,33 +11982,6 @@
         </is>
       </c>
       <c r="C146" s="16" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D146" s="16" t="n">
-        <v>503</v>
-      </c>
-      <c r="E146" s="16" t="n">
-        <v>91</v>
-      </c>
-      <c r="F146" s="16" t="n">
-        <v>914</v>
-      </c>
-      <c r="G146" s="16" t="n">
-        <v>274</v>
-      </c>
-      <c r="H146" s="16" t="n">
-        <v>183</v>
-      </c>
-      <c r="I146" s="16" t="n">
-        <v>457</v>
-      </c>
-      <c r="J146" s="16" t="n">
-        <v>137</v>
-      </c>
-      <c r="K146" s="16" t="n">
-        <v>91</v>
-      </c>
-      <c r="L146" s="16" t="n">
         <v>4570</v>
       </c>
       <c r="N146" s="17">
@@ -15140,33 +11996,6 @@
         </is>
       </c>
       <c r="C147" s="16" t="n">
-        <v>769</v>
-      </c>
-      <c r="D147" s="16" t="n">
-        <v>192</v>
-      </c>
-      <c r="E147" s="16" t="n">
-        <v>38</v>
-      </c>
-      <c r="F147" s="16" t="n">
-        <v>1462</v>
-      </c>
-      <c r="G147" s="16" t="n">
-        <v>423</v>
-      </c>
-      <c r="H147" s="16" t="n">
-        <v>308</v>
-      </c>
-      <c r="I147" s="16" t="n">
-        <v>462</v>
-      </c>
-      <c r="J147" s="16" t="n">
-        <v>115</v>
-      </c>
-      <c r="K147" s="16" t="n">
-        <v>77</v>
-      </c>
-      <c r="L147" s="16" t="n">
         <v>3846</v>
       </c>
       <c r="N147" s="17">
@@ -15181,33 +12010,6 @@
         </is>
       </c>
       <c r="C148" s="16" t="n">
-        <v>264</v>
-      </c>
-      <c r="D148" s="16" t="n">
-        <v>75</v>
-      </c>
-      <c r="E148" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="F148" s="16" t="n">
-        <v>339</v>
-      </c>
-      <c r="G148" s="16" t="n">
-        <v>94</v>
-      </c>
-      <c r="H148" s="16" t="n">
-        <v>75</v>
-      </c>
-      <c r="I148" s="16" t="n">
-        <v>678</v>
-      </c>
-      <c r="J148" s="16" t="n">
-        <v>207</v>
-      </c>
-      <c r="K148" s="16" t="n">
-        <v>132</v>
-      </c>
-      <c r="L148" s="16" t="n">
         <v>1883</v>
       </c>
       <c r="N148" s="17">
@@ -15222,33 +12024,6 @@
         </is>
       </c>
       <c r="C149" s="16" t="n">
-        <v>2066</v>
-      </c>
-      <c r="D149" s="16" t="n">
-        <v>516</v>
-      </c>
-      <c r="E149" s="16" t="n">
-        <v>74</v>
-      </c>
-      <c r="F149" s="16" t="n">
-        <v>2139</v>
-      </c>
-      <c r="G149" s="16" t="n">
-        <v>664</v>
-      </c>
-      <c r="H149" s="16" t="n">
-        <v>443</v>
-      </c>
-      <c r="I149" s="16" t="n">
-        <v>1033</v>
-      </c>
-      <c r="J149" s="16" t="n">
-        <v>295</v>
-      </c>
-      <c r="K149" s="16" t="n">
-        <v>148</v>
-      </c>
-      <c r="L149" s="16" t="n">
         <v>7378</v>
       </c>
       <c r="N149" s="17">
@@ -15263,33 +12038,6 @@
         </is>
       </c>
       <c r="C150" s="16" t="n">
-        <v>1099</v>
-      </c>
-      <c r="D150" s="16" t="n">
-        <v>288</v>
-      </c>
-      <c r="E150" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="F150" s="16" t="n">
-        <v>523</v>
-      </c>
-      <c r="G150" s="16" t="n">
-        <v>157</v>
-      </c>
-      <c r="H150" s="16" t="n">
-        <v>105</v>
-      </c>
-      <c r="I150" s="16" t="n">
-        <v>262</v>
-      </c>
-      <c r="J150" s="16" t="n">
-        <v>79</v>
-      </c>
-      <c r="K150" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="L150" s="16" t="n">
         <v>2617</v>
       </c>
       <c r="N150" s="17">
@@ -15304,33 +12052,6 @@
         </is>
       </c>
       <c r="C151" s="16" t="n">
-        <v>1103</v>
-      </c>
-      <c r="D151" s="16" t="n">
-        <v>276</v>
-      </c>
-      <c r="E151" s="16" t="n">
-        <v>55</v>
-      </c>
-      <c r="F151" s="16" t="n">
-        <v>2096</v>
-      </c>
-      <c r="G151" s="16" t="n">
-        <v>607</v>
-      </c>
-      <c r="H151" s="16" t="n">
-        <v>441</v>
-      </c>
-      <c r="I151" s="16" t="n">
-        <v>662</v>
-      </c>
-      <c r="J151" s="16" t="n">
-        <v>165</v>
-      </c>
-      <c r="K151" s="16" t="n">
-        <v>110</v>
-      </c>
-      <c r="L151" s="16" t="n">
         <v>5515</v>
       </c>
       <c r="N151" s="17">
@@ -15345,33 +12066,6 @@
         </is>
       </c>
       <c r="C152" s="16" t="n">
-        <v>687</v>
-      </c>
-      <c r="D152" s="16" t="n">
-        <v>180</v>
-      </c>
-      <c r="E152" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="F152" s="16" t="n">
-        <v>327</v>
-      </c>
-      <c r="G152" s="16" t="n">
-        <v>98</v>
-      </c>
-      <c r="H152" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="I152" s="16" t="n">
-        <v>164</v>
-      </c>
-      <c r="J152" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="K152" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="L152" s="16" t="n">
         <v>1636</v>
       </c>
       <c r="N152" s="17">
@@ -15386,33 +12080,6 @@
         </is>
       </c>
       <c r="C153" s="16" t="n">
-        <v>1004</v>
-      </c>
-      <c r="D153" s="16" t="n">
-        <v>251</v>
-      </c>
-      <c r="E153" s="16" t="n">
-        <v>36</v>
-      </c>
-      <c r="F153" s="16" t="n">
-        <v>1040</v>
-      </c>
-      <c r="G153" s="16" t="n">
-        <v>323</v>
-      </c>
-      <c r="H153" s="16" t="n">
-        <v>215</v>
-      </c>
-      <c r="I153" s="16" t="n">
-        <v>502</v>
-      </c>
-      <c r="J153" s="16" t="n">
-        <v>143</v>
-      </c>
-      <c r="K153" s="16" t="n">
-        <v>72</v>
-      </c>
-      <c r="L153" s="16" t="n">
         <v>3586</v>
       </c>
       <c r="N153" s="17">
@@ -15429,33 +12096,6 @@
       <c r="C154" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D154" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E154" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H154" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J154" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K154" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="16" t="n">
-        <v>0</v>
-      </c>
       <c r="N154" s="17">
         <f>ROW()</f>
         <v>154</v>
@@ -15468,33 +12108,6 @@
         </is>
       </c>
       <c r="C155" s="16" t="n">
-        <v>1225</v>
-      </c>
-      <c r="D155" s="16" t="n">
-        <v>306</v>
-      </c>
-      <c r="E155" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="F155" s="16" t="n">
-        <v>2328</v>
-      </c>
-      <c r="G155" s="16" t="n">
-        <v>674</v>
-      </c>
-      <c r="H155" s="16" t="n">
-        <v>490</v>
-      </c>
-      <c r="I155" s="16" t="n">
-        <v>735</v>
-      </c>
-      <c r="J155" s="16" t="n">
-        <v>184</v>
-      </c>
-      <c r="K155" s="16" t="n">
-        <v>123</v>
-      </c>
-      <c r="L155" s="16" t="n">
         <v>6126</v>
       </c>
       <c r="N155" s="17">
@@ -15509,33 +12122,6 @@
         </is>
       </c>
       <c r="C156" s="16" t="n">
-        <v>1284</v>
-      </c>
-      <c r="D156" s="16" t="n">
-        <v>336</v>
-      </c>
-      <c r="E156" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="F156" s="16" t="n">
-        <v>611</v>
-      </c>
-      <c r="G156" s="16" t="n">
-        <v>183</v>
-      </c>
-      <c r="H156" s="16" t="n">
-        <v>122</v>
-      </c>
-      <c r="I156" s="16" t="n">
-        <v>306</v>
-      </c>
-      <c r="J156" s="16" t="n">
-        <v>92</v>
-      </c>
-      <c r="K156" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="L156" s="16" t="n">
         <v>3056</v>
       </c>
       <c r="N156" s="17">
@@ -15550,33 +12136,6 @@
         </is>
       </c>
       <c r="C157" s="16" t="n">
-        <v>310</v>
-      </c>
-      <c r="D157" s="16" t="n">
-        <v>88</v>
-      </c>
-      <c r="E157" s="16" t="n">
-        <v>22</v>
-      </c>
-      <c r="F157" s="16" t="n">
-        <v>398</v>
-      </c>
-      <c r="G157" s="16" t="n">
-        <v>111</v>
-      </c>
-      <c r="H157" s="16" t="n">
-        <v>88</v>
-      </c>
-      <c r="I157" s="16" t="n">
-        <v>796</v>
-      </c>
-      <c r="J157" s="16" t="n">
-        <v>243</v>
-      </c>
-      <c r="K157" s="16" t="n">
-        <v>155</v>
-      </c>
-      <c r="L157" s="16" t="n">
         <v>2211</v>
       </c>
       <c r="N157" s="17">
@@ -15591,33 +12150,6 @@
         </is>
       </c>
       <c r="C158" s="16" t="n">
-        <v>1377</v>
-      </c>
-      <c r="D158" s="16" t="n">
-        <v>344</v>
-      </c>
-      <c r="E158" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="F158" s="16" t="n">
-        <v>1426</v>
-      </c>
-      <c r="G158" s="16" t="n">
-        <v>443</v>
-      </c>
-      <c r="H158" s="16" t="n">
-        <v>295</v>
-      </c>
-      <c r="I158" s="16" t="n">
-        <v>689</v>
-      </c>
-      <c r="J158" s="16" t="n">
-        <v>197</v>
-      </c>
-      <c r="K158" s="16" t="n">
-        <v>98</v>
-      </c>
-      <c r="L158" s="16" t="n">
         <v>4918</v>
       </c>
       <c r="N158" s="17">
@@ -15632,33 +12164,6 @@
         </is>
       </c>
       <c r="C159" s="16" t="n">
-        <v>1019</v>
-      </c>
-      <c r="D159" s="16" t="n">
-        <v>267</v>
-      </c>
-      <c r="E159" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="F159" s="16" t="n">
-        <v>485</v>
-      </c>
-      <c r="G159" s="16" t="n">
-        <v>146</v>
-      </c>
-      <c r="H159" s="16" t="n">
-        <v>97</v>
-      </c>
-      <c r="I159" s="16" t="n">
-        <v>243</v>
-      </c>
-      <c r="J159" s="16" t="n">
-        <v>73</v>
-      </c>
-      <c r="K159" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="L159" s="16" t="n">
         <v>2428</v>
       </c>
       <c r="N159" s="17">
@@ -15673,33 +12178,6 @@
         </is>
       </c>
       <c r="C160" s="16" t="n">
-        <v>6357</v>
-      </c>
-      <c r="D160" s="16" t="n">
-        <v>1589</v>
-      </c>
-      <c r="E160" s="16" t="n">
-        <v>318</v>
-      </c>
-      <c r="F160" s="16" t="n">
-        <v>12078</v>
-      </c>
-      <c r="G160" s="16" t="n">
-        <v>3496</v>
-      </c>
-      <c r="H160" s="16" t="n">
-        <v>2543</v>
-      </c>
-      <c r="I160" s="16" t="n">
-        <v>3814</v>
-      </c>
-      <c r="J160" s="16" t="n">
-        <v>954</v>
-      </c>
-      <c r="K160" s="16" t="n">
-        <v>636</v>
-      </c>
-      <c r="L160" s="16" t="n">
         <v>31785</v>
       </c>
       <c r="N160" s="17">
@@ -15715,42 +12193,6 @@
       </c>
       <c r="C161" s="18">
         <f>SUM(C119:C160)</f>
-        <v>61804</v>
-      </c>
-      <c r="D161" s="18">
-        <f>SUM(D119:D160)</f>
-        <v>15706</v>
-      </c>
-      <c r="E161" s="18">
-        <f>SUM(E119:E160)</f>
-        <v>2883</v>
-      </c>
-      <c r="F161" s="18">
-        <f>SUM(F119:F160)</f>
-        <v>81377</v>
-      </c>
-      <c r="G161" s="18">
-        <f>SUM(G119:G160)</f>
-        <v>23936</v>
-      </c>
-      <c r="H161" s="18">
-        <f>SUM(H119:H160)</f>
-        <v>17031</v>
-      </c>
-      <c r="I161" s="18">
-        <f>SUM(I119:I160)</f>
-        <v>34573</v>
-      </c>
-      <c r="J161" s="18">
-        <f>SUM(J119:J160)</f>
-        <v>9421</v>
-      </c>
-      <c r="K161" s="18">
-        <f>SUM(K119:K160)</f>
-        <v>5860</v>
-      </c>
-      <c r="L161" s="18">
-        <f>SUM(L119:L160)</f>
         <v>252591</v>
       </c>
       <c r="O161" s="2" t="inlineStr">

--- a/Intake_Mexico_v1.xlsx
+++ b/Intake_Mexico_v1.xlsx
@@ -12,8 +12,10 @@
     <sheet name="01. History Wind" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="02. EPI EQ" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="02. EPI Wind" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06. EQ Aggs" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07. Wind Aggs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08. Splits EQ" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="08. Splits Wind" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="06. EQ Aggs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="07. Wind Aggs" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -509,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AD119"/>
+  <dimension ref="B1:AK127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -528,16 +530,29 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="15" customWidth="1" min="25" max="25"/>
     <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="15" customWidth="1" min="32" max="32"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="15" customWidth="1" min="35" max="35"/>
+    <col width="15" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="15" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -577,7 +592,7 @@
           <t>Headers  →</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>Attributes  →</t>
         </is>
@@ -609,42 +624,42 @@
           <t>Incurred Losses</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="X5" s="6" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="Y5" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="S5" s="6" t="inlineStr">
+      <c r="Z5" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="T5" s="6" t="inlineStr">
+      <c r="AA5" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="U5" s="6" t="inlineStr">
+      <c r="AB5" s="6" t="inlineStr">
         <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="V5" s="6" t="inlineStr">
+      <c r="AC5" s="6" t="inlineStr">
         <is>
           <t>Premium basis</t>
         </is>
       </c>
-      <c r="W5" s="6" t="inlineStr">
+      <c r="AD5" s="6" t="inlineStr">
         <is>
           <t>Loss basis</t>
         </is>
       </c>
-      <c r="X5" s="6" t="inlineStr">
+      <c r="AE5" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -676,42 +691,42 @@
           <t>Incurred Losses</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="X6" s="6" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="Y6" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="S6" s="6" t="inlineStr">
+      <c r="Z6" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="T6" s="6" t="inlineStr">
+      <c r="AA6" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="U6" s="6" t="inlineStr">
+      <c r="AB6" s="6" t="inlineStr">
         <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="V6" s="6" t="inlineStr">
+      <c r="AC6" s="6" t="inlineStr">
         <is>
           <t>Premium basis</t>
         </is>
       </c>
-      <c r="W6" s="6" t="inlineStr">
+      <c r="AD6" s="6" t="inlineStr">
         <is>
           <t>Loss basis</t>
         </is>
       </c>
-      <c r="X6" s="6" t="inlineStr">
+      <c r="AE6" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -738,37 +753,37 @@
           <t>EPI</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="X7" s="6" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="Y7" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="S7" s="6" t="inlineStr">
+      <c r="Z7" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="T7" s="6" t="inlineStr">
+      <c r="AA7" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="U7" s="6" t="inlineStr">
+      <c r="AB7" s="6" t="inlineStr">
         <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="V7" s="6" t="inlineStr">
+      <c r="AC7" s="6" t="inlineStr">
         <is>
           <t>Premium basis</t>
         </is>
       </c>
-      <c r="W7" s="6" t="inlineStr">
+      <c r="AD7" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -795,37 +810,37 @@
           <t>EPI</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="X8" s="6" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="Y8" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="S8" s="6" t="inlineStr">
+      <c r="Z8" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="T8" s="6" t="inlineStr">
+      <c r="AA8" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="U8" s="6" t="inlineStr">
+      <c r="AB8" s="6" t="inlineStr">
         <is>
           <t>Year basis</t>
         </is>
       </c>
-      <c r="V8" s="6" t="inlineStr">
+      <c r="AC8" s="6" t="inlineStr">
         <is>
           <t>Premium basis</t>
         </is>
       </c>
-      <c r="W8" s="6" t="inlineStr">
+      <c r="AD8" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -894,75 +909,115 @@
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
+          <t>Res (optional)</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>Com (optional)</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>Ind (optional)</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>Building (optional)</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>Content (optional)</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>BI (optional)</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>Projects (optional)</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>Renewables (optional)</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
           <t>Total (optional)</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="X9" s="6" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="Y9" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="S9" s="6" t="inlineStr">
+      <c r="Z9" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="T9" s="6" t="inlineStr">
+      <c r="AA9" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="U9" s="6" t="inlineStr">
+      <c r="AB9" s="6" t="inlineStr">
         <is>
           <t>Exposure basis</t>
         </is>
       </c>
-      <c r="V9" s="6" t="inlineStr">
+      <c r="AC9" s="6" t="inlineStr">
         <is>
           <t>Zone scheme</t>
         </is>
       </c>
-      <c r="W9" s="6" t="inlineStr">
+      <c r="AD9" s="6" t="inlineStr">
         <is>
           <t>Coinsurance</t>
         </is>
       </c>
-      <c r="X9" s="6" t="inlineStr">
+      <c r="AE9" s="6" t="inlineStr">
         <is>
           <t>Deductible</t>
         </is>
       </c>
-      <c r="Y9" s="6" t="inlineStr">
+      <c r="AF9" s="6" t="inlineStr">
         <is>
           <t>Standard deductible</t>
         </is>
       </c>
-      <c r="Z9" s="6" t="inlineStr">
+      <c r="AG9" s="6" t="inlineStr">
         <is>
           <t>Limit basis</t>
         </is>
       </c>
-      <c r="AA9" s="6" t="inlineStr">
+      <c r="AH9" s="6" t="inlineStr">
         <is>
           <t>Multi-location</t>
         </is>
       </c>
-      <c r="AB9" s="6" t="inlineStr">
+      <c r="AI9" s="6" t="inlineStr">
         <is>
           <t>Includes fac</t>
         </is>
       </c>
-      <c r="AC9" s="6" t="inlineStr">
+      <c r="AJ9" s="6" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="AD9" s="6" t="inlineStr">
+      <c r="AK9" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -1001,167 +1056,292 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
+          <t>Building (optional)</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Content (optional)</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>BI (optional)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Projects (optional)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Renewables (optional)</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
           <t>Total (optional)</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="X10" s="6" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="Y10" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="S10" s="6" t="inlineStr">
+      <c r="Z10" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="T10" s="6" t="inlineStr">
+      <c r="AA10" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="U10" s="6" t="inlineStr">
+      <c r="AB10" s="6" t="inlineStr">
         <is>
           <t>Exposure basis</t>
         </is>
       </c>
-      <c r="V10" s="6" t="inlineStr">
+      <c r="AC10" s="6" t="inlineStr">
         <is>
           <t>Zone scheme</t>
         </is>
       </c>
-      <c r="W10" s="6" t="inlineStr">
+      <c r="AD10" s="6" t="inlineStr">
         <is>
           <t>Coinsurance</t>
         </is>
       </c>
-      <c r="X10" s="6" t="inlineStr">
+      <c r="AE10" s="6" t="inlineStr">
         <is>
           <t>Deductible</t>
         </is>
       </c>
-      <c r="Y10" s="6" t="inlineStr">
+      <c r="AF10" s="6" t="inlineStr">
         <is>
           <t>Standard deductible</t>
         </is>
       </c>
-      <c r="Z10" s="6" t="inlineStr">
+      <c r="AG10" s="6" t="inlineStr">
         <is>
           <t>Limit basis</t>
         </is>
       </c>
-      <c r="AA10" s="6" t="inlineStr">
+      <c r="AH10" s="6" t="inlineStr">
         <is>
           <t>Multi-location</t>
         </is>
       </c>
-      <c r="AB10" s="6" t="inlineStr">
+      <c r="AI10" s="6" t="inlineStr">
         <is>
           <t>Includes fac</t>
         </is>
       </c>
-      <c r="AC10" s="6" t="inlineStr">
+      <c r="AJ10" s="6" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="AD10" s="6" t="inlineStr">
+      <c r="AK10" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>08. Splits EQ</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>08 Splits EQ</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Building (optional)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Content (optional)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>BI (optional)</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Total (optional)</t>
+        </is>
+      </c>
+      <c r="X11" s="6" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="Y11" s="6" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="Z11" s="6" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="AA11" s="6" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="AB11" s="6" t="inlineStr">
+        <is>
+          <t>Exposure basis</t>
+        </is>
+      </c>
+      <c r="AC11" s="6" t="inlineStr">
+        <is>
+          <t>Includes fac</t>
+        </is>
+      </c>
+      <c r="AD11" s="6" t="inlineStr">
+        <is>
+          <t>As at</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>08. Splits Wind</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>08 Splits Wind</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Building (optional)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Content (optional)</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>BI (optional)</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Total (optional)</t>
+        </is>
+      </c>
+      <c r="X12" s="6" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="Y12" s="6" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="Z12" s="6" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="AA12" s="6" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="AB12" s="6" t="inlineStr">
+        <is>
+          <t>Exposure basis</t>
+        </is>
+      </c>
+      <c r="AC12" s="6" t="inlineStr">
+        <is>
+          <t>Includes fac</t>
+        </is>
+      </c>
+      <c r="AD12" s="6" t="inlineStr">
+        <is>
+          <t>As at</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>⟦INVENTORY⟧</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Holds</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>State</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Premium and loss history per section</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>implemented</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>EPI Projections</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Estimated premium income, N and N+1</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Large Losses</t>
+          <t>History</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Individual large claims, per-risk sections</t>
+          <t>Premium and loss history per section</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1173,17 +1353,17 @@
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Cat Losses</t>
+          <t>EPI Projections</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Catastrophe events, cat sections</t>
+          <t>Estimated premium income, N and N+1</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1195,17 +1375,17 @@
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Risk Profiles</t>
+          <t>Large Losses</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Banded exposure — the per-risk rating basis</t>
+          <t>Individual large claims, per-risk sections</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1217,17 +1397,17 @@
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>EQ Aggs</t>
+          <t>Cat Losses</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Earthquake sums insured per cat zone</t>
+          <t>Catastrophe events, cat sections</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1239,17 +1419,17 @@
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Wind Aggs</t>
+          <t>Risk Profiles</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Windstorm sums insured per cat zone</t>
+          <t>Banded exposure — the per-risk rating basis</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1261,83 +1441,83 @@
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Splits</t>
+          <t>EQ Aggs</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Occupancy x cover (Fire) or x Projects/Renewables (Eng.)</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>axes settled, measures open</t>
+          <t>Earthquake sums insured per cat zone</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Rate Development</t>
+          <t>Wind Aggs</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Rate change history — optional</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>outstanding</t>
+          <t>Windstorm sums insured per cat zone</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Triangles</t>
+          <t>Splits</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Loss development triangles</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>outstanding</t>
+          <t>The cedent's book split — sums insured, one block per section</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>09</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Exchange rates</t>
+          <t>Rate Development</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>FX rates for conversion between currencies</t>
+          <t>Rate change history — optional</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -1349,286 +1529,306 @@
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Triangles</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Loss development triangles</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Exchange rates</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>FX rates for conversion between currencies</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Collected step-2 blocks — written, never read</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>outstanding</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="2" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Every dataset the tool knows, whether or not this pack carries it. The register above lists what is here; ⟦SECTIONS⟧ says which roles each section expects, so a missing sheet reads as structure rather than as a gap.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>⟦SECTIONS⟧</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="7" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>Datasets</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="6" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Earthquake</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>01, 02, 06</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="6" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 06, 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Hurricane</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>01, 02, 07</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="2" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 07, 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Either peril can be bought alone or both together, and the covered books need not be the same — so no rule compares 06 with 07.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="3" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>⟦ZONES⟧</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="7" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Scheme</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Zones</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="6" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Mexico EQ</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13a, 13b, 14a, 14b, 14c, 14d, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 48</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="6" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Mexico Wind</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="2" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>The complete zoning. This cedent returns every zone, so step 1 already shows all of them; where one lists only the zones it has exposure in, step 2 completes the rest with 0 — an absent zone reads as 'no data', a zero reads as 'nothing there'.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="3" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>⟦GLOBAL⟧</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="7" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Actual year</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Treaty type</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Mexico property cat</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Cedent</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Aseguradora Ejemplo SA</t>
-        </is>
+          <t>Actual year</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Loss share warning</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="n">
-        <v>0.2</v>
+          <t>Treaty type</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Mexico property cat</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="4" t="inlineStr">
         <is>
+          <t>Cedent</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Aseguradora Ejemplo SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Loss share warning</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="4" t="inlineStr">
+        <is>
           <t>Rate change warning</t>
         </is>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C52" s="10" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="2" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Rate change warning is the movement in premium per unit of exposure beyond which the growth block raises a warning (§10.4).</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="3" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="7" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Incurred Losses</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>EPI</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -1640,19 +1840,19 @@
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Zone</t>
+          <t>Incurred Losses</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>EPI</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -1664,31 +1864,31 @@
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Res Building</t>
+          <t>Zone</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Res Content</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Res BI</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -1700,7 +1900,7 @@
     <row r="65">
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Com Building</t>
+          <t>Res Building</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -1712,7 +1912,7 @@
     <row r="66">
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Com Content</t>
+          <t>Res Content</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -1724,7 +1924,7 @@
     <row r="67">
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Com BI</t>
+          <t>Res BI</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -1736,7 +1936,7 @@
     <row r="68">
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Ind Building</t>
+          <t>Com Building</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -1748,7 +1948,7 @@
     <row r="69">
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Ind Content</t>
+          <t>Com Content</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -1760,7 +1960,7 @@
     <row r="70">
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Ind BI</t>
+          <t>Com BI</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -1772,7 +1972,7 @@
     <row r="71">
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Res</t>
+          <t>Ind Building</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -1784,7 +1984,7 @@
     <row r="72">
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Com</t>
+          <t>Ind Content</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -1796,352 +1996,366 @@
     <row r="73">
       <c r="B73" s="4" t="inlineStr">
         <is>
+          <t>Ind BI</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Com</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="4" t="inlineStr">
+        <is>
           <t>Ind</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>⟦VOCABULARY⟧</t>
-        </is>
-      </c>
-    </row>
     <row r="77">
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>Permitted values</t>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>100% | ceded only</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>1 | 1,000 | 1,000,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>Exposure basis</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>Renewables</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>Zone scheme</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>Mexico EQ | Mexico Wind</t>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Coinsurance</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>deducted | not deducted</t>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Permitted values</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Deductible</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>deducted | not deducted</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Limit basis</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>full sum insured | per risk limit | per location limit</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Multi-location</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>split by location | allocated to main zone | duplicated in each zone</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Includes fac</t>
+          <t>Share basis</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>yes | no</t>
+          <t>100% | ceded only</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="4" t="inlineStr">
         <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>1 | 1,000 | 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Exposure basis</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Sum Insured | EML | PML | MPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Zone scheme</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Mexico EQ | Mexico Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Coinsurance</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>deducted | not deducted</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Deductible</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>deducted | not deducted</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Limit basis</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>full sum insured | per risk limit | per location limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Multi-location</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>split by location | allocated to main zone | duplicated in each zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Includes fac</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>yes | no</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" s="3" t="inlineStr">
+    <row r="101">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="7" t="inlineStr">
+    <row r="102">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C102" s="7" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="11" t="n">
+    <row r="103">
+      <c r="B103" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="11" t="n">
+    <row r="104">
+      <c r="B104" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="B97" s="11" t="n">
+    <row r="105">
+      <c r="B105" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="B98" s="11" t="n">
+    <row r="106">
+      <c r="B106" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>at inception</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="B99" s="11" t="n">
+    <row r="107">
+      <c r="B107" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>at expiry</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>'at inception' and 'at expiry' order the three versions of an aggregate: the nine-month estimate of N, then the first and the last day of N+1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>⟦AXES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>Axis</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>Categories</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>06 EQ Aggs</t>
-        </is>
-      </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>Res, Com, Ind</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>06 EQ Aggs</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>Cover</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>Building, Content, BI</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>07 Wind Aggs</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>Res, Com, Ind</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>The buckets of a dataset are the product of its axes: earthquake is occupancy × cover and has nine, hurricane declares occupancy alone and has three.</t>
+          <t>'at inception' and 'at expiry' order the three versions of an aggregate: the nine-month estimate of N, then the first and the last day of N+1.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>⟦SPLITS⟧</t>
+          <t>⟦AXES⟧</t>
         </is>
       </c>
     </row>
@@ -2158,29 +2372,14 @@
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>From</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>Share</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Categories</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>07 Wind Aggs</t>
+          <t>06 EQ Aggs</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
@@ -2188,44 +2387,26 @@
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr"/>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>Res</t>
-        </is>
-      </c>
-      <c r="F113" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>Cedent book split, 30.09.2025</t>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Res, Com, Ind</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>07 Wind Aggs</t>
+          <t>06 EQ Aggs</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="D114" s="4" t="inlineStr"/>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>Com</t>
-        </is>
-      </c>
-      <c r="F114" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t>Cedent book split, 30.09.2025</t>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Building, Content, BI</t>
         </is>
       </c>
     </row>
@@ -2240,83 +2421,210 @@
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr"/>
-      <c r="E115" s="4" t="inlineStr">
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Res, Com, Ind</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>The buckets of a dataset are the product of its axes: earthquake is occupancy × cover and has nine, hurricane declares occupancy alone and has three.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>⟦SPLITS⟧</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Renewables</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
         <is>
           <t>Ind</t>
         </is>
       </c>
-      <c r="F115" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>Cedent book split, 30.09.2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" s="4" t="inlineStr">
+      <c r="F121" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>House convention</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="C116" s="5" t="inlineStr">
+      <c r="C122" s="5" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>Com</t>
+        </is>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>House convention</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F123" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>House convention</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
         <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="E124" s="4" t="inlineStr">
         <is>
           <t>Com</t>
         </is>
       </c>
-      <c r="F116" s="10" t="n">
+      <c r="F124" s="10" t="n">
         <v>0.75</v>
       </c>
-      <c r="G116" s="4" t="inlineStr">
+      <c r="G124" s="4" t="inlineStr">
         <is>
           <t>House convention</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="B117" s="4" t="inlineStr">
+    <row r="125">
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D125" s="4" t="inlineStr">
         <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
+      <c r="E125" s="4" t="inlineStr">
         <is>
           <t>Ind</t>
         </is>
       </c>
-      <c r="F117" s="10" t="n">
+      <c r="F125" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="G117" s="4" t="inlineStr">
+      <c r="G125" s="4" t="inlineStr">
         <is>
           <t>House convention</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="B119" s="2" t="inlineStr">
+    <row r="127">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Ratios applied where the cedent reports at a coarser level. A blank 'From' distributes a whole axis; a filled one re-splits a category that arrived merged. 'Source' is not decoration — a ratio from the cedent's own prior submission and one borrowed from another book are both assumptions, but not equally good ones.</t>
         </is>
@@ -3236,6 +3544,526 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>08. Book split — Earthquake section</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Sums insured for the whole book. 06/07 read only ratios from this, so its scale and currency need not match theirs — only its own consistency matters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Section = Earthquake</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Currency = MXN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Scale = 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Share basis = 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Exposure basis = Sum Insured</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Includes fac = yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>As at = 30.09.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Ocupación</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Edificio</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Contenido</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Pérdida de beneficios</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Suma</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>← source header, never read</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Header_1</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>← extraction row: blanks mean 'not extracted'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>41200</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>10800</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>1640</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>53640</v>
+      </c>
+      <c r="H12" s="18">
+        <f>ROW()</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Com</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>38600</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>11900</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>8100</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>58600</v>
+      </c>
+      <c r="H13" s="18">
+        <f>ROW()</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>22400</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>7050</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>4900</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>34350</v>
+      </c>
+      <c r="H14" s="18">
+        <f>ROW()</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C15" s="19">
+        <f>SUM(C12:C14)</f>
+        <v>102200</v>
+      </c>
+      <c r="D15" s="19">
+        <f>SUM(D12:D14)</f>
+        <v>29750</v>
+      </c>
+      <c r="E15" s="19">
+        <f>SUM(E12:E14)</f>
+        <v>14640</v>
+      </c>
+      <c r="F15" s="19">
+        <f>SUM(F12:F14)</f>
+        <v>146590</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: excluded from extraction, reused as control</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Info_1 = H</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>08. Book split — Hurricane section</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Sums insured for the whole book. 06/07 read only ratios from this, so its scale and currency need not match theirs — only its own consistency matters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Section = Hurricane</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Currency = MXN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Scale = 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Share basis = 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Exposure basis = Sum Insured</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Includes fac = yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>As at = 30.09.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Ocupación</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Edificio</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Contenido</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Pérdida de beneficios</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Suma</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>← source header, never read</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Header_1</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>← extraction row: blanks mean 'not extracted'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Res</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>28900</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>7600</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>37650</v>
+      </c>
+      <c r="H12" s="18">
+        <f>ROW()</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Com</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>31400</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>9700</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>6600</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>47700</v>
+      </c>
+      <c r="H13" s="18">
+        <f>ROW()</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>15100</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>4750</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>23150</v>
+      </c>
+      <c r="H14" s="18">
+        <f>ROW()</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C15" s="19">
+        <f>SUM(C12:C14)</f>
+        <v>75400</v>
+      </c>
+      <c r="D15" s="19">
+        <f>SUM(D12:D14)</f>
+        <v>22050</v>
+      </c>
+      <c r="E15" s="19">
+        <f>SUM(E12:E14)</f>
+        <v>11050</v>
+      </c>
+      <c r="F15" s="19">
+        <f>SUM(F12:F14)</f>
+        <v>108500</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: excluded from extraction, reused as control</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Info_1 = H</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10384,7 +11212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Intake_Mexico_v1.xlsx
+++ b/Intake_Mexico_v1.xlsx
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Rate change history — optional</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>outstanding</t>
+          <t>The rate change a submission claims — the UW's own sheet</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
